--- a/docs/testing/PROJECT TEST CASES CAA 021026.xlsx
+++ b/docs/testing/PROJECT TEST CASES CAA 021026.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J254"/>
+  <dimension ref="A1:J257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7154,8 +7154,7 @@
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>The rejection is blocked with a message that a reason is required; the request remains Pending
-## E06-S05</t>
+          <t>The rejection is blocked with a message that a reason is required; the request remains Pending</t>
         </is>
       </c>
     </row>
@@ -7165,347 +7164,510 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
+          <t>E06-S04</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>E06-S04 - Scenario 4 (Booking decision recorded; T-66, T-67)</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>2 - Happy Path</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>TC_E06S04_04</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>Verify that an approved venue booking should be recorded with the actor, action, affected records, and time</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>A booking request for Venue Z is pending</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>1. As Venue Staff, approve the booking request
+2. Sign in as the Event Coordinator permitted to view the affected event
+3. Open the event Activity log
+4. Locate the completed booking action and compare its actor, action, booking/event identifiers and timestamp with the test database</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>Venue: Venue Z | Action: Approve Booking</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>An entry is recorded with the actor, action ("Booking Approved"), the affected booking/event, and a timestamp
+Transferred from TC_E14S02_03 by T-67 on 2 October 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>E06-S04</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>E06-S04 - Scenario 4 (Booking decision recorded; T-66, T-67)</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>2 - Happy Path</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>TC_E06S04_05</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>Verify that a rejected venue booking should be recorded with the actor, action, affected records, and time</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>A booking request for Venue Z is pending</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>1. As Venue Staff, reject the booking request with reason "Venue unavailable for maintenance"
+2. Sign in as the Event Coordinator permitted to view the affected event
+3. Open the event Activity log
+4. Locate the completed booking action and compare its actor, action, booking/event identifiers and timestamp with the test database</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>Venue: Venue Z | Action: Reject Booking | Reason: Venue unavailable for maintenance</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>An entry is recorded with the actor, action ("Booking Rejected"), the affected booking/event, and a timestamp
+Transferred from TC_E14S02_06 by T-67 on 2 October 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>E06-S04</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>E06-S04 - Scenario 4 (Booking decision recorded; T-66, T-67)</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>2 - Happy Path</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>TC_E06S04_06</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>Verify that a released venue booking should be recorded with the actor, action, affected records, and time</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>Venue Z has a confirmed booking for event "Annual Tech Summit"; the Coordinator is authorised to cancel that event and the E10-S04 cancellation/release workflow is available</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>1. As the authorised Coordinator, cancel the event through E10-S04 so its confirmed Venue Z booking is released
+2. Sign in as the Event Coordinator permitted to view the affected event
+3. Open the event Activity log
+4. Locate the completed booking action and compare its actor, action, booking/event identifiers and timestamp with the test database</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>Venue: Venue Z | Action: Release Booking | Event: Annual Tech Summit</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>An entry is recorded with the actor, action ("Booking Released"), the affected booking/event, and a timestamp
+Transferred from TC_E14S02_07 by T-67 on 2 October 2026.
+## E06-S05</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>E06-S05</t>
         </is>
       </c>
-      <c r="C129" s="2" t="inlineStr">
+      <c r="C132" s="2" t="inlineStr">
         <is>
           <t>E06-S05 · Scenario 2 (Slot already held or booked)</t>
         </is>
       </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>4 - Negative (business rule)</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>TC_E06S05_01</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Verify that a second tentative hold on the same venue and period is refused</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr">
         <is>
           <t>Orchid Hall has an active tentative hold for 2026-12-01 09:00 to 11:00 against event EVT-1005. Coordinator coord_b@connectsphere.com is planning event EVT-1006</t>
         </is>
       </c>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as coord_b@connectsphere.com
  2. Open the venue calendar for Orchid Hall on 2026-12-01
  3. Attempt to place a tentative hold for 09:00–11:00 against EVT-1006</t>
         </is>
       </c>
-      <c r="I129" s="2" t="inlineStr">
+      <c r="I132" s="2" t="inlineStr">
         <is>
           <t>Existing hold: EVT-1005, 09:00–11:00 · Requested: EVT-1006, same period</t>
         </is>
       </c>
-      <c r="J129" s="2" t="inlineStr">
+      <c r="J132" s="2" t="inlineStr">
         <is>
           <t>The hold is refused and the existing hold against EVT-1005 is identified. The calendar continues to show the period as Tentative for one event only
 ## E06-S06</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="n">
+    <row r="133">
+      <c r="A133" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B130" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t>E06-S06</t>
         </is>
       </c>
-      <c r="C130" s="2" t="inlineStr">
+      <c r="C133" s="2" t="inlineStr">
         <is>
           <t>E06-S06 - Scenario 1 (Overlapping approval blocked)</t>
         </is>
       </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>TC_E06S06_01</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to approve a request that overlaps an existing confirmed booking for the same venue should be blocked with the conflicting booking identified</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr">
         <is>
           <t>"Riverside Hall" has a confirmed booking for "Charity Run" on 15/01/2027, 09:00-17:00. A second pending request for "Riverside Hall" on 15/01/2027, 14:00-18:00 exists for event "Product Expo 2026"</t>
         </is>
       </c>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>1. Log in as venue_staff_1@connectsphere.com
   2. Open the pending request for "Product Expo 2026"
   3. Attempt to click "Approve"</t>
         </is>
       </c>
-      <c r="I130" s="2" t="inlineStr">
+      <c r="I133" s="2" t="inlineStr">
         <is>
           <t>Existing confirmed booking: Charity Run, 15/01/2027 09:00-17:00 | Conflicting request: Product Expo 2026, 15/01/2027 14:00-18:00</t>
         </is>
       </c>
-      <c r="J130" s="2" t="inlineStr">
+      <c r="J133" s="2" t="inlineStr">
         <is>
           <t>Approval is blocked, and the message identifies the existing confirmed "Charity Run" booking as the conflict</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="n">
+    <row r="134">
+      <c r="A134" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B131" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
         <is>
           <t>E06-S06</t>
         </is>
       </c>
-      <c r="C131" s="2" t="inlineStr">
+      <c r="C134" s="2" t="inlineStr">
         <is>
           <t>E06-S06 - Scenario 2 (Competing request flagged)</t>
         </is>
       </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>TC_E06S06_02</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Verify that approving one of two pending requests for the same venue and overlapping times should flag the other as conflicting</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr">
         <is>
           <t>Two pending requests exist for "Riverside Hall" on 20/01/2027, both 09:00-12:00: Request A ("Tech Conference 2026") and Request B ("Product Expo 2026")</t>
         </is>
       </c>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>1. Log in as venue_staff_1@connectsphere.com
   2. Approve Request A ("Tech Conference 2026")
   3. Open Request B ("Product Expo 2026")</t>
         </is>
       </c>
-      <c r="I131" s="2" t="inlineStr">
+      <c r="I134" s="2" t="inlineStr">
         <is>
           <t>Request A: Tech Conference 2026 (approved) | Request B: Product Expo 2026 (same venue, overlapping time)</t>
         </is>
       </c>
-      <c r="J131" s="2" t="inlineStr">
+      <c r="J134" s="2" t="inlineStr">
         <is>
           <t>Request B is now flagged as conflicting and cannot be approved until the conflict is resolved</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="n">
+    <row r="135">
+      <c r="A135" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B132" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t>E06-S06</t>
         </is>
       </c>
-      <c r="C132" s="2" t="inlineStr">
+      <c r="C135" s="2" t="inlineStr">
         <is>
           <t>E06-S06 - Scenario 3 (Simultaneous approval fails safely)</t>
         </is>
       </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>TC_E06S06_03</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Verify that if another Venue Staff member approves a conflicting request moments earlier, a simultaneous approval attempt should fail safely and inform the user the venue has just been taken</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr">
         <is>
           <t>Two pending requests exist for "Riverside Hall" on 25/01/2027, overlapping times. venue_staff_2@connectsphere.com approves one of them a moment before venue_staff_1@connectsphere.com processes the other</t>
         </is>
       </c>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>1. As venue_staff_2@connectsphere.com, approve Request A for "Riverside Hall" on 25/01/2027
   2. Immediately as venue_staff_1@connectsphere.com, attempt to approve the conflicting Request B for the same venue and overlapping time</t>
         </is>
       </c>
-      <c r="I132" s="2" t="inlineStr">
+      <c r="I135" s="2" t="inlineStr">
         <is>
           <t>Request A approved by venue_staff_2@connectsphere.com just before venue_staff_1@connectsphere.com's attempt on Request B</t>
         </is>
       </c>
-      <c r="J132" s="2" t="inlineStr">
+      <c r="J135" s="2" t="inlineStr">
         <is>
           <t>venue_staff_1@connectsphere.com's approval attempt fails safely, with a message stating the venue has just been taken by another approval</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="n">
+    <row r="136">
+      <c r="A136" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B133" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>E06-S06</t>
         </is>
       </c>
-      <c r="C133" s="2" t="inlineStr">
+      <c r="C136" s="2" t="inlineStr">
         <is>
           <t>E06-S06 · Scenario 1 (Overlapping approval blocked)</t>
         </is>
       </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (adjacent, must not conflict)</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>TC_E06S06_04</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Verify that a booking beginning exactly when another ends is not treated as a conflict</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr">
         <is>
           <t>Venue Orchid Hall has a confirmed booking for 2026-11-10 09:00:00 to 2026-11-10 11:00:00. A pending request exists for the same venue for 2026-11-10 11:00:00 to 2026-11-10 13:00:00</t>
         </is>
       </c>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as Venue Staff
  2. Open the pending request for 11:00–13:00
  3. Approve it</t>
         </is>
       </c>
-      <c r="I133" s="2" t="inlineStr">
+      <c r="I136" s="2" t="inlineStr">
         <is>
           <t>Existing: 09:00–11:00 · Requested: 11:00–13:00 · Shared boundary: 11:00</t>
         </is>
       </c>
-      <c r="J133" s="2" t="inlineStr">
+      <c r="J136" s="2" t="inlineStr">
         <is>
           <t>The approval succeeds and both bookings show as Confirmed on the venue calendar. Ranges are half-open, so touching at the boundary is not an overlap</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="n">
+    <row r="137">
+      <c r="A137" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B134" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>E06-S06</t>
         </is>
       </c>
-      <c r="C134" s="2" t="inlineStr">
+      <c r="C137" s="2" t="inlineStr">
         <is>
           <t>E06-S06 · Scenario 1 (Overlapping approval blocked)</t>
         </is>
       </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (one minute of overlap, must conflict)</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>TC_E06S06_05</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Verify that a booking overlapping an existing one by a single minute is blocked</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr">
         <is>
           <t>Venue Orchid Hall has a confirmed booking for 2026-11-10 09:00:00 to 2026-11-10 11:00:00. A pending request exists for the same venue for 2026-11-10 10:59:00 to 2026-11-10 13:00:00</t>
         </is>
       </c>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as Venue Staff
  2. Open the pending request for 10:59–13:00
  3. Attempt to approve it</t>
         </is>
       </c>
-      <c r="I134" s="2" t="inlineStr">
+      <c r="I137" s="2" t="inlineStr">
         <is>
           <t>Existing: 09:00–11:00 · Requested: 10:59–13:00 · Overlap: 1 minute</t>
         </is>
       </c>
-      <c r="J134" s="2" t="inlineStr">
+      <c r="J137" s="2" t="inlineStr">
         <is>
           <t>Approval is blocked and the conflicting 09:00–11:00 booking is identified. The venue never holds two confirmed bookings over the same period</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="n">
+    <row r="138">
+      <c r="A138" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B135" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t>E07-S01</t>
         </is>
       </c>
-      <c r="C135" s="2" t="inlineStr">
+      <c r="C138" s="2" t="inlineStr">
         <is>
           <t>E07-S01 - Scenario 1 (Item added and reservable)</t>
         </is>
       </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>TC_E07S01_01</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Verify that saving a new equipment item with its full details should make it available for reservation</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr">
         <is>
           <t>tech_support_1@connectsphere.com is signed in; equipment item "Wireless Microphone" does not yet exist</t>
         </is>
       </c>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to "Add Equipment"
   2. Enter Type: "Wireless Microphone", Description: "Handheld, UHF", Quantity: 10, Location: "Main Storage", Operational Status: "Working"
@@ -7513,52 +7675,52 @@
   4. Log in as an Event Coordinator and check equipment availability for "Wireless Microphone"</t>
         </is>
       </c>
-      <c r="I135" s="2" t="inlineStr">
+      <c r="I138" s="2" t="inlineStr">
         <is>
           <t>Item: Wireless Microphone | Quantity: 10 | Location: Main Storage | Status: Working</t>
         </is>
       </c>
-      <c r="J135" s="2" t="inlineStr">
+      <c r="J138" s="2" t="inlineStr">
         <is>
           <t>The item is saved and appears as available for reservation, with 10 units free</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="n">
+    <row r="139">
+      <c r="A139" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B136" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>E07-S01</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
+      <c r="C139" s="2" t="inlineStr">
         <is>
           <t>E07-S01 - Scenario 2 (Quantity drop flags reservations)</t>
         </is>
       </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>TC_E07S01_02</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Verify that reducing an item's quantity below the amount already reserved for upcoming events should flag the affected reservations and notify the relevant Coordinators</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr">
         <is>
           <t>"Wireless Microphone" (quantity 10) has 6 units reserved for an upcoming event of "Tech Conference 2026", assigned to coordinator_1@connectsphere.com</t>
         </is>
       </c>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open equipment item "Wireless Microphone"
@@ -7566,52 +7728,52 @@
   4. Save</t>
         </is>
       </c>
-      <c r="I136" s="2" t="inlineStr">
+      <c r="I139" s="2" t="inlineStr">
         <is>
           <t>Quantity: 10 -&gt; 4 | Existing reservation: 6 units</t>
         </is>
       </c>
-      <c r="J136" s="2" t="inlineStr">
+      <c r="J139" s="2" t="inlineStr">
         <is>
           <t>The 6-unit reservation is flagged for review since it now exceeds total stock, and coordinator_1@connectsphere.com is notified</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="n">
+    <row r="140">
+      <c r="A140" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B137" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
         <is>
           <t>E07-S01</t>
         </is>
       </c>
-      <c r="C137" s="2" t="inlineStr">
+      <c r="C140" s="2" t="inlineStr">
         <is>
           <t>E07-S01 - Scenario 3 (Item retired)</t>
         </is>
       </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>TC_E07S01_03</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Verify that retiring an item with no future reservations should remove it from availability checks while retaining its past reservations</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr">
         <is>
           <t>Equipment item "Old Projector" has no future reservations; it has 2 past (completed) reservations on record</t>
         </is>
       </c>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open equipment item "Old Projector"
@@ -7620,52 +7782,52 @@
   5. Check availability for "Old Projector" as an Event Coordinator</t>
         </is>
       </c>
-      <c r="I137" s="2" t="inlineStr">
+      <c r="I140" s="2" t="inlineStr">
         <is>
           <t>Item: Old Projector (no future reservations)</t>
         </is>
       </c>
-      <c r="J137" s="2" t="inlineStr">
+      <c r="J140" s="2" t="inlineStr">
         <is>
           <t>"Old Projector" no longer appears in availability checks; its 2 past reservations remain retained and viewable in historical records</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="n">
+    <row r="141">
+      <c r="A141" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B138" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t>E07-S01</t>
         </is>
       </c>
-      <c r="C138" s="2" t="inlineStr">
+      <c r="C141" s="2" t="inlineStr">
         <is>
           <t>E07-S01 (checklist: update equipment attributes)</t>
         </is>
       </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>TC_E07S01_04</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Verify that updating an existing equipment item's attributes should save the changes</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr">
         <is>
           <t>Equipment item "Wireless Microphone" exists with Location: "Main Storage"</t>
         </is>
       </c>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open equipment item "Wireless Microphone"
@@ -7673,53 +7835,53 @@
   4. Click "Save"</t>
         </is>
       </c>
-      <c r="I138" s="2" t="inlineStr">
+      <c r="I141" s="2" t="inlineStr">
         <is>
           <t>Location: Main Storage -&gt; Annex Storage</t>
         </is>
       </c>
-      <c r="J138" s="2" t="inlineStr">
+      <c r="J141" s="2" t="inlineStr">
         <is>
           <t>The updated Location value is saved and shown when the item record is reopened
 ## E07-S02</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="n">
+    <row r="142">
+      <c r="A142" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B139" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>E07-S02</t>
         </is>
       </c>
-      <c r="C139" s="2" t="inlineStr">
+      <c r="C142" s="2" t="inlineStr">
         <is>
           <t>E07-S02 - Scenario 1 (Equipment recorded against an event)</t>
         </is>
       </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>TC_E07S02_01</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Verify that adding equipment items with quantities to a event of an approved event should save the request and notify Technical Support Staff</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Conference 2026" is Approved; the event has no equipment requested yet</t>
         </is>
       </c>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the event of "Tech Conference 2026"
@@ -7728,52 +7890,52 @@
   5. Check tech_support_1@connectsphere.com's notifications</t>
         </is>
       </c>
-      <c r="I139" s="2" t="inlineStr">
+      <c r="I142" s="2" t="inlineStr">
         <is>
           <t>the event equipment: Wireless Microphone x2, Projector x1</t>
         </is>
       </c>
-      <c r="J139" s="2" t="inlineStr">
+      <c r="J142" s="2" t="inlineStr">
         <is>
           <t>The equipment request is saved against the event, and tech_support_1@connectsphere.com is notified</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="n">
+    <row r="143">
+      <c r="A143" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B140" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>E07-S02</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr">
+      <c r="C143" s="2" t="inlineStr">
         <is>
           <t>E07-S02 - Scenario 2 (Request exceeds total stock)</t>
         </is>
       </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>TC_E07S02_02</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Verify that requesting more of an item than ConnectSphere owns in total should warn that the request cannot be met from existing stock</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr">
         <is>
           <t>"Wireless Microphone" has a total stock of 10 units</t>
         </is>
       </c>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open a event of "Tech Conference 2026"
@@ -7781,52 +7943,52 @@
   4. Save</t>
         </is>
       </c>
-      <c r="I140" s="2" t="inlineStr">
+      <c r="I143" s="2" t="inlineStr">
         <is>
           <t>Requested quantity: 15 | Total stock: 10</t>
         </is>
       </c>
-      <c r="J140" s="2" t="inlineStr">
+      <c r="J143" s="2" t="inlineStr">
         <is>
           <t>A warning is shown that the request (15 units) cannot be met from existing stock (10 units)</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="n">
+    <row r="144">
+      <c r="A144" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B141" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>E07-S02</t>
         </is>
       </c>
-      <c r="C141" s="2" t="inlineStr">
+      <c r="C144" s="2" t="inlineStr">
         <is>
           <t>E07-S02 - Scenario 3 (Events independent of each other)</t>
         </is>
       </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>TC_E07S02_03</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Verify that recording equipment for one event should leave a different event's equipment unaffected</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr">
         <is>
           <t>Coordinator coordinator_1@connectsphere.com manages two separate events, "Tech Conference 2026" and "Charity Run", neither with equipment requested yet</t>
         </is>
       </c>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open "Tech Conference 2026" and add "Projector" x 1
@@ -7834,52 +7996,52 @@
   4. Open "Charity Run" and check its equipment list</t>
         </is>
       </c>
-      <c r="I141" s="2" t="inlineStr">
+      <c r="I144" s="2" t="inlineStr">
         <is>
           <t>"Tech Conference 2026": Projector x1 added | "Charity Run": unchanged</t>
         </is>
       </c>
-      <c r="J141" s="2" t="inlineStr">
+      <c r="J144" s="2" t="inlineStr">
         <is>
           <t>"Tech Conference 2026" shows "Projector x1"; "Charity Run"'s equipment list remains empty, unaffected by the other event's request</t>
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="n">
+    <row r="145">
+      <c r="A145" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B142" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>E07-S02</t>
         </is>
       </c>
-      <c r="C142" s="2" t="inlineStr">
+      <c r="C145" s="2" t="inlineStr">
         <is>
           <t>E07-S02 (checklist: amend or remove equipment request before reservation)</t>
         </is>
       </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>TC_E07S02_04</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Verify that amending or removing an equipment request before it is reserved should update or clear the request accordingly</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr">
         <is>
           <t>the event of "Tech Conference 2026" has an unreserved equipment request: "Wireless Microphone" x 2</t>
         </is>
       </c>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the event's equipment request
@@ -7888,208 +8050,208 @@
   5. Save</t>
         </is>
       </c>
-      <c r="I142" s="2" t="inlineStr">
+      <c r="I145" s="2" t="inlineStr">
         <is>
           <t>Quantity change: 2 -&gt; 3, then removed entirely</t>
         </is>
       </c>
-      <c r="J142" s="2" t="inlineStr">
+      <c r="J145" s="2" t="inlineStr">
         <is>
           <t>After step 3, the request shows "Wireless Microphone x3"; after step 5, the request no longer includes "Wireless Microphone"
 ## E07-S03</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="n">
+    <row r="146">
+      <c r="A146" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B143" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>E07-S03</t>
         </is>
       </c>
-      <c r="C143" s="2" t="inlineStr">
+      <c r="C146" s="2" t="inlineStr">
         <is>
           <t>E07-S03 - Scenario 1 (Reserved and faulty stock excluded)</t>
         </is>
       </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>TC_E07S03_01</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Verify that checking availability for a period with other reservations should exclude those reservations and any damaged or under-maintenance items from the free quantity</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr">
         <is>
           <t>"Wireless Microphone" has total stock 10; 3 units are reserved for another event on 15/11/2026, 09:00-12:00; 2 units are marked damaged</t>
         </is>
       </c>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Check availability for "Wireless Microphone" on 15/11/2026, 09:00-12:00</t>
         </is>
       </c>
-      <c r="I143" s="2" t="inlineStr">
+      <c r="I146" s="2" t="inlineStr">
         <is>
           <t>Total stock: 10 | Reserved: 3 | Damaged: 2</t>
         </is>
       </c>
-      <c r="J143" s="2" t="inlineStr">
+      <c r="J146" s="2" t="inlineStr">
         <is>
           <t>The free quantity shown is 5 (10 minus 3 reserved minus 2 damaged)</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="n">
+    <row r="147">
+      <c r="A147" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
         <is>
           <t>E07-S03</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
+      <c r="C147" s="2" t="inlineStr">
         <is>
           <t>E07-S03 - Scenario 2 (Location does not affect availability)</t>
         </is>
       </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>TC_E07S03_02</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Verify that an item free for the requested date and time but located at another venue should still be shown as available, with no transport allowance applied</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr">
         <is>
           <t>"Projector" is free for 15/11/2026, 09:00-12:00, but is currently located at "Grand Ballroom" rather than the requested venue</t>
         </is>
       </c>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Check availability for "Projector" on 15/11/2026, 09:00-12:00 for a event at "Riverside Hall"</t>
         </is>
       </c>
-      <c r="I144" s="2" t="inlineStr">
+      <c r="I147" s="2" t="inlineStr">
         <is>
           <t>Item location: Grand Ballroom | Requested venue: Riverside Hall</t>
         </is>
       </c>
-      <c r="J144" s="2" t="inlineStr">
+      <c r="J147" s="2" t="inlineStr">
         <is>
           <t>"Projector" is shown as available with its full free quantity; no transport time or allowance is added to the availability check</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="n">
+    <row r="148">
+      <c r="A148" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>E07-S03</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr">
+      <c r="C148" s="2" t="inlineStr">
         <is>
           <t>E07-S03 - Scenario 3 (Non-overlapping events share an item)</t>
         </is>
       </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>TC_E07S03_03</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Verify that two events requiring the same item at non-overlapping times on the same day should both show it as free</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr">
         <is>
           <t>"Tech Conference 2026" the event (09:00-12:00) and the event (14:00-17:00) both require "Wireless Microphone", with no other reservations that day</t>
         </is>
       </c>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Check availability for "Wireless Microphone" during the event's time (09:00-12:00)
   3. Check availability for "Wireless Microphone" during the event's time (14:00-17:00)</t>
         </is>
       </c>
-      <c r="I145" s="2" t="inlineStr">
+      <c r="I148" s="2" t="inlineStr">
         <is>
           <t>the event: 09:00-12:00 | the event: 14:00-17:00 (same day, non-overlapping)</t>
         </is>
       </c>
-      <c r="J145" s="2" t="inlineStr">
+      <c r="J148" s="2" t="inlineStr">
         <is>
           <t>"Wireless Microphone" shows its full free quantity for both the event's and the event's time windows
 ## E07-S04</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="n">
+    <row r="149">
+      <c r="A149" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B146" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="C146" s="2" t="inlineStr">
+      <c r="C149" s="2" t="inlineStr">
         <is>
           <t>E07-S04 - Scenario 1 (Full reservation recorded)</t>
         </is>
       </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>TC_E07S04_01</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Verify that reserving the requested quantity when sufficient equipment is free should record the reservation and notify the Event Coordinator</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr">
         <is>
           <t>the event of "Tech Conference 2026" requested "Wireless Microphone" x 2; 5 units are free for that period</t>
         </is>
       </c>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open the equipment request for the event
@@ -8098,52 +8260,52 @@
   5. Check coordinator_1@connectsphere.com's notifications</t>
         </is>
       </c>
-      <c r="I146" s="2" t="inlineStr">
+      <c r="I149" s="2" t="inlineStr">
         <is>
           <t>Reserved: Wireless Microphone x2 (5 free)</t>
         </is>
       </c>
-      <c r="J146" s="2" t="inlineStr">
+      <c r="J149" s="2" t="inlineStr">
         <is>
           <t>The reservation is recorded against the event, and coordinator_1@connectsphere.com receives a confirmation showing the event's date/time, item, and quantity</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="n">
+    <row r="150">
+      <c r="A150" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B147" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="C147" s="2" t="inlineStr">
+      <c r="C150" s="2" t="inlineStr">
         <is>
           <t>E07-S04 - Scenario 2 (Partial reservation and shortfall)</t>
         </is>
       </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>TC_E07S04_02</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Verify that recording a partial reservation when only part of the requested quantity is free should notify the Coordinator of the shortfall</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr">
         <is>
           <t>the event of "Tech Conference 2026" requested "Projector" x 3; only 2 units are free for that period</t>
         </is>
       </c>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open the equipment request for the event
@@ -8151,103 +8313,103 @@
   4. Confirm</t>
         </is>
       </c>
-      <c r="I147" s="2" t="inlineStr">
+      <c r="I150" s="2" t="inlineStr">
         <is>
           <t>Requested: 3 | Reserved (partial): 2 | Shortfall: 1</t>
         </is>
       </c>
-      <c r="J147" s="2" t="inlineStr">
+      <c r="J150" s="2" t="inlineStr">
         <is>
           <t>coordinator_1@connectsphere.com is notified of the shortfall, showing 2 reserved and 1 outstanding unit of "Projector"</t>
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="n">
+    <row r="151">
+      <c r="A151" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
+      <c r="C151" s="2" t="inlineStr">
         <is>
           <t>E07-S04 - Scenario 3 (Fully committed item shows nothing free)</t>
         </is>
       </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (exactly at)</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>TC_E07S04_03</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Verify that once an item becomes fully committed, a subsequent availability check for that period should show no free quantity</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr">
         <is>
           <t>"Portable Stage" (total stock 2) has both units fully reserved for the period 20/11/2026, 09:00-17:00</t>
         </is>
       </c>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Check availability for "Portable Stage" on 20/11/2026, 09:00-17:00</t>
         </is>
       </c>
-      <c r="I148" s="2" t="inlineStr">
+      <c r="I151" s="2" t="inlineStr">
         <is>
           <t>Portable Stage: 2 total, 2 reserved</t>
         </is>
       </c>
-      <c r="J148" s="2" t="inlineStr">
+      <c r="J151" s="2" t="inlineStr">
         <is>
           <t>The availability check shows 0 free units of "Portable Stage" for that period</t>
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="n">
+    <row r="152">
+      <c r="A152" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B149" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr">
+      <c r="C152" s="2" t="inlineStr">
         <is>
           <t>E07-S04 - Scenario 4 (Reservation released)</t>
         </is>
       </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>TC_E07S04_04</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Verify that releasing a reservation when a event is cancelled or the equipment is no longer required should return the quantity to the available pool</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr">
         <is>
           <t>the event of "Tech Conference 2026" has a reservation of "Wireless Microphone" x 2</t>
         </is>
       </c>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open the reservation for the event
@@ -8256,52 +8418,52 @@
   5. Check availability for "Wireless Microphone" for that period</t>
         </is>
       </c>
-      <c r="I149" s="2" t="inlineStr">
+      <c r="I152" s="2" t="inlineStr">
         <is>
           <t>Released reservation: Wireless Microphone x2</t>
         </is>
       </c>
-      <c r="J149" s="2" t="inlineStr">
+      <c r="J152" s="2" t="inlineStr">
         <is>
           <t>The 2 units are returned to the available pool, increasing the free quantity for that period by 2</t>
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="n">
+    <row r="153">
+      <c r="A153" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B150" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="C150" s="2" t="inlineStr">
+      <c r="C153" s="2" t="inlineStr">
         <is>
           <t>E07-S04 · Scenario 1 (Full reservation recorded)</t>
         </is>
       </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (just below)</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>TC_E07S04_05</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Verify that requesting one fewer than the free quantity produces a full reservation and leaves the remainder free</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr">
         <is>
           <t>Equipment Projector-HD has total quantity 10. Six units are reserved for other events overlapping EVT-1003, leaving 4 free. Event EVT-1003 has an equipment request for 3 units</t>
         </is>
       </c>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as Technical Support Staff
  2. Open the equipment request for EVT-1003
@@ -8309,52 +8471,52 @@
  4. Re-check availability for the same period</t>
         </is>
       </c>
-      <c r="I150" s="2" t="inlineStr">
+      <c r="I153" s="2" t="inlineStr">
         <is>
           <t>Free quantity: 4 · Requested: 3</t>
         </is>
       </c>
-      <c r="J150" s="2" t="inlineStr">
+      <c r="J153" s="2" t="inlineStr">
         <is>
           <t>A reservation of 3 is recorded with status Reserved, not Partial. Availability for the period now shows 1 free. Confirmation of the event is not blocked by this reservation</t>
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="n">
+    <row r="154">
+      <c r="A154" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B151" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
+      <c r="C154" s="2" t="inlineStr">
         <is>
           <t>E07-S04 · Scenario 1 (Full reservation recorded)</t>
         </is>
       </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (exactly at)</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>TC_E07S04_06</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Verify that requesting exactly the free quantity produces a full reservation and leaves nothing free</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr">
         <is>
           <t>Equipment Projector-HD has total quantity 10. Six units are reserved for other events overlapping EVT-1003, leaving 4 free. Event EVT-1003 has an equipment request for 4 units</t>
         </is>
       </c>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as Technical Support Staff
  2. Open the equipment request for EVT-1003
@@ -8362,52 +8524,52 @@
  4. Re-check availability for the same period</t>
         </is>
       </c>
-      <c r="I151" s="2" t="inlineStr">
+      <c r="I154" s="2" t="inlineStr">
         <is>
           <t>Free quantity: 4 · Requested: 4</t>
         </is>
       </c>
-      <c r="J151" s="2" t="inlineStr">
+      <c r="J154" s="2" t="inlineStr">
         <is>
           <t>A reservation of 4 is recorded with status Reserved. Availability for the period shows 0 free. No shortfall notification is sent</t>
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="n">
+    <row r="155">
+      <c r="A155" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B152" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="C152" s="2" t="inlineStr">
+      <c r="C155" s="2" t="inlineStr">
         <is>
           <t>E07-S04 · Scenario 2 (Partial reservation and shortfall) · E08-S03 Scenario 3</t>
         </is>
       </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (just above)</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>TC_E07S04_07</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Verify that requesting one more than the free quantity produces a partial reservation that blocks confirmation</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr">
         <is>
           <t>Equipment Projector-HD has total quantity 10. Six units are reserved for other events overlapping EVT-1003, leaving 4 free. Event EVT-1003 has an equipment request for 5 units. Event EVT-1003 already has a confirmed venue booking</t>
         </is>
       </c>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as Technical Support Staff
  2. Open the equipment request for EVT-1003
@@ -8415,53 +8577,53 @@
  4. Sign in as the assigned Event Coordinator and attempt to confirm the event</t>
         </is>
       </c>
-      <c r="I152" s="2" t="inlineStr">
+      <c r="I155" s="2" t="inlineStr">
         <is>
           <t>Free quantity: 4 · Requested: 5 · Reserved: 4 · Outstanding: 1</t>
         </is>
       </c>
-      <c r="J152" s="2" t="inlineStr">
+      <c r="J155" s="2" t="inlineStr">
         <is>
           <t>The reservation is recorded with status Partial. The Coordinator is notified of an outstanding quantity of 1. Confirmation is blocked and the outstanding item is listed against event EVT-1003
 ## E07-S05</t>
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="n">
+    <row r="156">
+      <c r="A156" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B153" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t>E07-S05</t>
         </is>
       </c>
-      <c r="C153" s="2" t="inlineStr">
+      <c r="C156" s="2" t="inlineStr">
         <is>
           <t>E07-S05 - Scenario 1 (Item marked unavailable)</t>
         </is>
       </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>TC_E07S05_01</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Verify that marking an item with no reservations in the period unavailable, with a reason and a period, should exclude it from availability checks for that period</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr">
         <is>
           <t>Equipment item "HD Camera" has no reservations between 01/12/2026 and 05/12/2026</t>
         </is>
       </c>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open equipment item "HD Camera"
@@ -8471,52 +8633,52 @@
   6. Check availability for "HD Camera" on 03/12/2026</t>
         </is>
       </c>
-      <c r="I153" s="2" t="inlineStr">
+      <c r="I156" s="2" t="inlineStr">
         <is>
           <t>Period: 01/12/2026-05/12/2026 | Reason: Sensor repair</t>
         </is>
       </c>
-      <c r="J153" s="2" t="inlineStr">
+      <c r="J156" s="2" t="inlineStr">
         <is>
           <t>"HD Camera" shows 0 available units for any date within 01/12/2026-05/12/2026</t>
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="n">
+    <row r="157">
+      <c r="A157" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B154" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
         <is>
           <t>E07-S05</t>
         </is>
       </c>
-      <c r="C154" s="2" t="inlineStr">
+      <c r="C157" s="2" t="inlineStr">
         <is>
           <t>E07-S05 - Scenario 2 (Reserved item flags its events)</t>
         </is>
       </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>TC_E07S05_02</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>Verify that marking an item unavailable while it is reserved for an upcoming event should flag the affected event and notify its Coordinator</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr">
         <is>
           <t>"HD Camera" is reserved for an upcoming event of "Tech Conference 2026", assigned to coordinator_1@connectsphere.com</t>
         </is>
       </c>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open equipment item "HD Camera"
@@ -8524,52 +8686,52 @@
   4. Save</t>
         </is>
       </c>
-      <c r="I154" s="2" t="inlineStr">
+      <c r="I157" s="2" t="inlineStr">
         <is>
           <t>Affected event: Tech Conference 2026 event with HD Camera reserved</t>
         </is>
       </c>
-      <c r="J154" s="2" t="inlineStr">
+      <c r="J157" s="2" t="inlineStr">
         <is>
           <t>The affected event is flagged, and coordinator_1@connectsphere.com is notified that its reserved "HD Camera" is now unavailable</t>
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="n">
+    <row r="158">
+      <c r="A158" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B155" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t>E07-S05</t>
         </is>
       </c>
-      <c r="C155" s="2" t="inlineStr">
+      <c r="C158" s="2" t="inlineStr">
         <is>
           <t>E07-S05 (checklist: return item to service)</t>
         </is>
       </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>TC_E07S05_03</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>Verify that returning an item to service should restore it to availability checks</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr">
         <is>
           <t>"HD Camera" is currently marked unavailable for 01/12/2026-05/12/2026 with reason "Sensor repair"</t>
         </is>
       </c>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open equipment item "HD Camera"
@@ -8578,53 +8740,53 @@
   5. Check availability for "HD Camera" on 03/12/2026</t>
         </is>
       </c>
-      <c r="I155" s="2" t="inlineStr">
+      <c r="I158" s="2" t="inlineStr">
         <is>
           <t>Item: HD Camera (returning to service)</t>
         </is>
       </c>
-      <c r="J155" s="2" t="inlineStr">
+      <c r="J158" s="2" t="inlineStr">
         <is>
           <t>"HD Camera" now shows as available again for 03/12/2026
 ## E07-S06</t>
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="n">
+    <row r="159">
+      <c r="A159" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B156" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
         <is>
           <t>E07-S06</t>
         </is>
       </c>
-      <c r="C156" s="2" t="inlineStr">
+      <c r="C159" s="2" t="inlineStr">
         <is>
           <t>E07-S06 - Scenario 1 (Support request recorded)</t>
         </is>
       </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>TC_E07S06_01</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>Verify that submitting a technical support request describing the support needed and the times should notify Technical Support Staff and record it against the event</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr">
         <is>
           <t>the event of "Tech Conference 2026" requires on-site technical support</t>
         </is>
       </c>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the event of "Tech Conference 2026"
@@ -8634,104 +8796,104 @@
   6. Check tech_support_1@connectsphere.com's notifications</t>
         </is>
       </c>
-      <c r="I156" s="2" t="inlineStr">
+      <c r="I159" s="2" t="inlineStr">
         <is>
           <t>Support description: "1 AV technician for the full event" | Times: 09:00-12:00</t>
         </is>
       </c>
-      <c r="J156" s="2" t="inlineStr">
+      <c r="J159" s="2" t="inlineStr">
         <is>
           <t>The request is recorded against the event, and tech_support_1@connectsphere.com is notified</t>
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="n">
+    <row r="160">
+      <c r="A160" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B157" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t>E07-S06</t>
         </is>
       </c>
-      <c r="C157" s="2" t="inlineStr">
+      <c r="C160" s="2" t="inlineStr">
         <is>
           <t>E07-S06 - Scenario 2 (Request accepted before venue confirmed)</t>
         </is>
       </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>TC_E07S06_02</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>Verify that submitting a technical support request before the venue is confirmed should be accepted and reviewed alongside venue identification</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr">
         <is>
           <t>the event of "Tech Conference 2026" does not yet have a confirmed venue</t>
         </is>
       </c>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the event of "Tech Conference 2026" (no confirmed venue)
   3. Submit a technical support request describing "1 sound technician" for the event's planned times</t>
         </is>
       </c>
-      <c r="I157" s="2" t="inlineStr">
+      <c r="I160" s="2" t="inlineStr">
         <is>
           <t>the event: no confirmed venue yet</t>
         </is>
       </c>
-      <c r="J157" s="2" t="inlineStr">
+      <c r="J160" s="2" t="inlineStr">
         <is>
           <t>The technical support request is accepted and recorded, without waiting for the venue to be confirmed first</t>
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="n">
+    <row r="161">
+      <c r="A161" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B158" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t>E07-S06</t>
         </is>
       </c>
-      <c r="C158" s="2" t="inlineStr">
+      <c r="C161" s="2" t="inlineStr">
         <is>
           <t>E07-S06 - Scenario 3 (Event marked as needing none)</t>
         </is>
       </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>TC_E07S06_03</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>Verify that marking a event as needing no technical support should create no request and not block confirmation on staff assignment</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr">
         <is>
           <t>A event of "Charity Run" needs no on-site technical support</t>
         </is>
       </c>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the event of "Charity Run"
@@ -8739,53 +8901,53 @@
   4. Save</t>
         </is>
       </c>
-      <c r="I158" s="2" t="inlineStr">
+      <c r="I161" s="2" t="inlineStr">
         <is>
           <t>Event: Charity Run's event | Technical Support: Not Required</t>
         </is>
       </c>
-      <c r="J158" s="2" t="inlineStr">
+      <c r="J161" s="2" t="inlineStr">
         <is>
           <t>No technical support request is created for the event, and later event confirmation is not blocked waiting for a staff assignment
 ## E07-S07</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="n">
+    <row r="162">
+      <c r="A162" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B159" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t>E07-S07</t>
         </is>
       </c>
-      <c r="C159" s="2" t="inlineStr">
+      <c r="C162" s="2" t="inlineStr">
         <is>
           <t>E07-S07 - Scenario 1 (Available colleague assigned)</t>
         </is>
       </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>TC_E07S07_01</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>Verify that a colleague with no conflicting assignment during the event's required time period should be successfully assigned</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr">
         <is>
           <t>the event of "Tech Conference 2026" (09:00-12:00) has an open technical support request. tech_support_2@connectsphere.com has no assignment overlapping 09:00-12:00 on that date</t>
         </is>
       </c>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open the technical support request for the event
@@ -8793,155 +8955,155 @@
   4. Confirm</t>
         </is>
       </c>
-      <c r="I159" s="2" t="inlineStr">
+      <c r="I162" s="2" t="inlineStr">
         <is>
           <t>Assignee: tech_support_2@connectsphere.com | Event time: 09:00-12:00</t>
         </is>
       </c>
-      <c r="J159" s="2" t="inlineStr">
+      <c r="J162" s="2" t="inlineStr">
         <is>
           <t>The assignment succeeds; tech_support_2@connectsphere.com is notified and the assignment appears on their schedule</t>
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="n">
+    <row r="163">
+      <c r="A163" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B160" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
         <is>
           <t>E07-S07</t>
         </is>
       </c>
-      <c r="C160" s="2" t="inlineStr">
+      <c r="C163" s="2" t="inlineStr">
         <is>
           <t>E07-S07 (checklist: see assignment on schedule)</t>
         </is>
       </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>TC_E07S07_02</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>Verify that the assignment should be reflected on the assigned staff member's schedule once made</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr">
         <is>
           <t>tech_support_2@connectsphere.com has just been assigned to the event of "Tech Conference 2026" (09:00-12:00)</t>
         </is>
       </c>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_2@connectsphere.com
   2. Open "My Schedule"</t>
         </is>
       </c>
-      <c r="I160" s="2" t="inlineStr">
+      <c r="I163" s="2" t="inlineStr">
         <is>
           <t>Assignment: the event, Tech Conference 2026, 09:00-12:00</t>
         </is>
       </c>
-      <c r="J160" s="2" t="inlineStr">
+      <c r="J163" s="2" t="inlineStr">
         <is>
           <t>The schedule shows the assignment to the event of "Tech Conference 2026" at 09:00-12:00</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="n">
+    <row r="164">
+      <c r="A164" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B161" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
         <is>
           <t>E07-S07</t>
         </is>
       </c>
-      <c r="C161" s="2" t="inlineStr">
+      <c r="C164" s="2" t="inlineStr">
         <is>
           <t>E07-S07 - Scenario 2 (Overlapping assignment blocked)</t>
         </is>
       </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>TC_E07S07_03</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>Verify that assigning a colleague who has an overlapping assignment should be blocked, with the conflicting event identified</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr">
         <is>
           <t>tech_support_2@connectsphere.com is already assigned to a event of "Charity Run" from 10:00-13:00 on the same date. the event of "Tech Conference 2026" runs 09:00-12:00 on that date and needs a technician assigned</t>
         </is>
       </c>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open the technical support request for the event of "Tech Conference 2026"
   3. Attempt to assign tech_support_2@connectsphere.com</t>
         </is>
       </c>
-      <c r="I161" s="2" t="inlineStr">
+      <c r="I164" s="2" t="inlineStr">
         <is>
           <t>Existing assignment: Charity Run event, 10:00-13:00 | New attempted assignment: Tech Conference 2026 the event, 09:00-12:00 (overlaps)</t>
         </is>
       </c>
-      <c r="J161" s="2" t="inlineStr">
+      <c r="J164" s="2" t="inlineStr">
         <is>
           <t>The assignment is blocked, and the message identifies the conflicting "Charity Run" event as the reason</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="n">
+    <row r="165">
+      <c r="A165" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B162" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
         <is>
           <t>E07-S07</t>
         </is>
       </c>
-      <c r="C162" s="2" t="inlineStr">
+      <c r="C165" s="2" t="inlineStr">
         <is>
           <t>E07-S07 - Scenario 3 (Assignment removed)</t>
         </is>
       </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>TC_E07S07_04</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>Verify that removing an existing assignment from a staff member's schedule should free up that slot</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr">
         <is>
           <t>tech_support_2@connectsphere.com is assigned to the event of "Tech Conference 2026"</t>
         </is>
       </c>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open the assignment for the event
@@ -8950,104 +9112,104 @@
   5. Check tech_support_2@connectsphere.com's schedule</t>
         </is>
       </c>
-      <c r="I162" s="2" t="inlineStr">
+      <c r="I165" s="2" t="inlineStr">
         <is>
           <t>Assignment removed: tech_support_2@connectsphere.com, the event</t>
         </is>
       </c>
-      <c r="J162" s="2" t="inlineStr">
+      <c r="J165" s="2" t="inlineStr">
         <is>
           <t>The assignment no longer appears on tech_support_2@connectsphere.com's schedule, and the slot is free for reassignment</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="2" t="n">
+    <row r="166">
+      <c r="A166" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B163" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
         <is>
           <t>E07-S07</t>
         </is>
       </c>
-      <c r="C163" s="2" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
         <is>
           <t>E07-S07 - Scenario 4 (Replacement assigned under same check)</t>
         </is>
       </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>TC_E07S07_05</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>Verify that assigning a replacement colleague after removing an assignment should be subject to the same conflict check used for new assignments</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr">
         <is>
           <t>The assignment for the event of "Tech Conference 2026" has just been removed from tech_support_2@connectsphere.com. tech_support_3@connectsphere.com already has a conflicting assignment during the event's time</t>
         </is>
       </c>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open the now-unassigned technical support request for the event
   3. Attempt to assign tech_support_3@connectsphere.com as a replacement</t>
         </is>
       </c>
-      <c r="I163" s="2" t="inlineStr">
+      <c r="I166" s="2" t="inlineStr">
         <is>
           <t>Replacement candidate: tech_support_3@connectsphere.com (has a conflicting assignment)</t>
         </is>
       </c>
-      <c r="J163" s="2" t="inlineStr">
+      <c r="J166" s="2" t="inlineStr">
         <is>
           <t>The replacement assignment is blocked using the same conflict check as a new assignment, with the conflicting event identified</t>
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="n">
+    <row r="167">
+      <c r="A167" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B164" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
         <is>
           <t>E07-S07</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr">
+      <c r="C167" s="2" t="inlineStr">
         <is>
           <t>E07-S07 (checklist: staff notified when assigned or removed)</t>
         </is>
       </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>3 - Cross-cutting (notification consistency)</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>TC_E07S07_06</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>Verify that the assigned staff member should receive a notification when they are assigned to, or removed from, an event</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr">
         <is>
           <t>tech_support_2@connectsphere.com is about to be assigned to, and later removed from, the event of "Tech Conference 2026"</t>
         </is>
       </c>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>1. As tech_support_1@connectsphere.com, assign tech_support_2@connectsphere.com to the event
   2. Check tech_support_2@connectsphere.com's notifications
@@ -9055,52 +9217,52 @@
   4. Check tech_support_2@connectsphere.com's notifications again</t>
         </is>
       </c>
-      <c r="I164" s="2" t="inlineStr">
+      <c r="I167" s="2" t="inlineStr">
         <is>
           <t>Actions: assign, then remove</t>
         </is>
       </c>
-      <c r="J164" s="2" t="inlineStr">
+      <c r="J167" s="2" t="inlineStr">
         <is>
           <t>tech_support_2@connectsphere.com receives a notification for the assignment, and a separate notification for the removal</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2" t="n">
+    <row r="168">
+      <c r="A168" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B165" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>E08-S03</t>
         </is>
       </c>
-      <c r="C165" s="2" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
         <is>
           <t>E08-S03 - Scenario 1 (All arrangements complete, event confirmed)</t>
         </is>
       </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>TC_E08S03_01</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>Verify that confirming an event where every event has a confirmed venue and full equipment reservation should set its status to Confirmed and notify the Organiser</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr">
         <is>
           <t>Event "Charity Run" has one event with a confirmed venue booking (Riverside Hall) and its full requested equipment reserved, and requires no technical support</t>
         </is>
       </c>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Charity Run"
@@ -9108,260 +9270,260 @@
   4. Check the status and organiser_a@clienta.com's notifications</t>
         </is>
       </c>
-      <c r="I165" s="2" t="inlineStr">
+      <c r="I168" s="2" t="inlineStr">
         <is>
           <t>Event: Charity Run (venue confirmed, equipment fully reserved, no tech support needed)</t>
         </is>
       </c>
-      <c r="J165" s="2" t="inlineStr">
+      <c r="J168" s="2" t="inlineStr">
         <is>
           <t>The status becomes "Confirmed", and organiser_a@clienta.com is notified with the confirmed details</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="2" t="n">
+    <row r="169">
+      <c r="A169" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B166" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
         <is>
           <t>E08-S03</t>
         </is>
       </c>
-      <c r="C166" s="2" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
         <is>
           <t>E08-S03 - Scenario 2 (Missing venue blocks confirmation)</t>
         </is>
       </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>TC_E08S03_02</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to confirm an event while a event is missing a confirmed venue should be blocked with the outstanding event named</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Conference 2026" has the event with a confirmed venue, but the event has no confirmed venue yet</t>
         </is>
       </c>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Tech Conference 2026"
   3. Click "Confirm Event"</t>
         </is>
       </c>
-      <c r="I166" s="2" t="inlineStr">
+      <c r="I169" s="2" t="inlineStr">
         <is>
           <t>the event: venue confirmed | the event: no venue</t>
         </is>
       </c>
-      <c r="J166" s="2" t="inlineStr">
+      <c r="J169" s="2" t="inlineStr">
         <is>
           <t>Confirmation is blocked; the message lists "the event" as missing a confirmed venue</t>
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="2" t="n">
+    <row r="170">
+      <c r="A170" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B167" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>E08-S03</t>
         </is>
       </c>
-      <c r="C167" s="2" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
         <is>
           <t>E08-S03 - Scenario 3 (Partial equipment blocks confirmation)</t>
         </is>
       </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>TC_E08S03_03</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to confirm an event while a event has only a partial equipment reservation should be blocked with the outstanding quantity shown</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Conference 2026" has all events with confirmed venues, but the event's "Projector" reservation is partial (2 of 3 requested)</t>
         </is>
       </c>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Tech Conference 2026"
   3. Click "Confirm Event"</t>
         </is>
       </c>
-      <c r="I167" s="2" t="inlineStr">
+      <c r="I170" s="2" t="inlineStr">
         <is>
           <t>the event: Projector reserved 2 of 3 requested</t>
         </is>
       </c>
-      <c r="J167" s="2" t="inlineStr">
+      <c r="J170" s="2" t="inlineStr">
         <is>
           <t>Confirmation is blocked; the message shows the event's outstanding quantity of 1 "Projector" unit</t>
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="2" t="n">
+    <row r="171">
+      <c r="A171" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B168" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
         <is>
           <t>E08-S03</t>
         </is>
       </c>
-      <c r="C168" s="2" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
         <is>
           <t>E08-S03 - Scenario 5 (Outstanding support assignment blocks confirmation)</t>
         </is>
       </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>TC_E08S03_04</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to confirm an event while a event's requested technical support has no staff assigned should be blocked</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr">
         <is>
           <t>All events of "Tech Conference 2026" have confirmed venues and full equipment, but the event's technical support request has no staff assigned</t>
         </is>
       </c>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Tech Conference 2026"
   3. Click "Confirm Event"</t>
         </is>
       </c>
-      <c r="I168" s="2" t="inlineStr">
+      <c r="I171" s="2" t="inlineStr">
         <is>
           <t>the event: technical support requested, no staff assigned</t>
         </is>
       </c>
-      <c r="J168" s="2" t="inlineStr">
+      <c r="J171" s="2" t="inlineStr">
         <is>
           <t>Confirmation is blocked due to the event's outstanding technical support assignment</t>
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="2" t="n">
+    <row r="172">
+      <c r="A172" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>E08-S03</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
         <is>
           <t>E08-S03 - Scenario 6 (Organiser sees confirmed arrangements)</t>
         </is>
       </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>TC_E08S03_05</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>Verify that once an event is confirmed, the Organiser should see the confirmed venue, date, time and arrangements for every event</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr">
         <is>
           <t>Event "Charity Run" has just been confirmed, with venue Riverside Hall, date 15/01/2027, time 09:00-17:00</t>
         </is>
       </c>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open the confirmed event "Charity Run"</t>
         </is>
       </c>
-      <c r="I169" s="2" t="inlineStr">
+      <c r="I172" s="2" t="inlineStr">
         <is>
           <t>Confirmed venue: Riverside Hall | Date: 15/01/2027 | Time: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J169" s="2" t="inlineStr">
+      <c r="J172" s="2" t="inlineStr">
         <is>
           <t>The Organiser sees the confirmed venue (Riverside Hall), date (15/01/2027), time (09:00-17:00), and full arrangements for the event
 ## E08-S04</t>
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="2" t="n">
+    <row r="173">
+      <c r="A173" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B170" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
         <is>
           <t>E08-S04</t>
         </is>
       </c>
-      <c r="C170" s="2" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
         <is>
           <t>E08-S04 - Scenario 1 (Reverted with a recorded reason)</t>
         </is>
       </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>TC_E08S04_01</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>Verify that reverting a Confirmed event to Planning with a recorded reason should update its status and notify the Organiser with the reason</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr">
         <is>
           <t>Event "Leadership Summit" has status "Confirmed"</t>
         </is>
       </c>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Leadership Summit"
@@ -9370,52 +9532,52 @@
   5. Confirm</t>
         </is>
       </c>
-      <c r="I170" s="2" t="inlineStr">
+      <c r="I173" s="2" t="inlineStr">
         <is>
           <t>Reason: "Venue reported a plumbing issue"</t>
         </is>
       </c>
-      <c r="J170" s="2" t="inlineStr">
+      <c r="J173" s="2" t="inlineStr">
         <is>
           <t>The status changes to "Planning", and organiser_a@clienta.com is notified with the reason "Venue reported a plumbing issue"</t>
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2" t="n">
+    <row r="174">
+      <c r="A174" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>E08-S04</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
+      <c r="C174" s="2" t="inlineStr">
         <is>
           <t>E08-S04 - Scenario 2 (Registered Attendees notified)</t>
         </is>
       </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>TC_E08S04_02</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>Verify that reverting a Confirmed event with registered Attendees should notify them that arrangements are being revised</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr">
         <is>
           <t>Event "Leadership Summit" has status "Confirmed" with attendee_a@example.com registered</t>
         </is>
       </c>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Leadership Summit"
@@ -9423,413 +9585,413 @@
   4. Check attendee_a@example.com's notifications</t>
         </is>
       </c>
-      <c r="I171" s="2" t="inlineStr">
+      <c r="I174" s="2" t="inlineStr">
         <is>
           <t>Registered Attendee: attendee_a@example.com</t>
         </is>
       </c>
-      <c r="J171" s="2" t="inlineStr">
+      <c r="J174" s="2" t="inlineStr">
         <is>
           <t>attendee_a@example.com receives a notification that arrangements for "Leadership Summit" are being revised</t>
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="2" t="n">
+    <row r="175">
+      <c r="A175" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B172" s="2" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
         <is>
           <t>E08-S04</t>
         </is>
       </c>
-      <c r="C172" s="2" t="inlineStr">
+      <c r="C175" s="2" t="inlineStr">
         <is>
           <t>E08-S04 - Scenario 3 (No automatic reversion)</t>
         </is>
       </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>TC_E08S04_03</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>Verify that an arrangement breaking on a Confirmed event should not automatically revert its status; the affected arrangement should instead be flagged</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr">
         <is>
           <t>Event "Leadership Summit" has status "Confirmed"; its venue booking has just been flagged due to a broken arrangement, but no one has reverted the event</t>
         </is>
       </c>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open event "Leadership Summit"
   3. Check the event status and the flagged arrangement</t>
         </is>
       </c>
-      <c r="I172" s="2" t="inlineStr">
+      <c r="I175" s="2" t="inlineStr">
         <is>
           <t>Flagged arrangement: venue booking</t>
         </is>
       </c>
-      <c r="J172" s="2" t="inlineStr">
+      <c r="J175" s="2" t="inlineStr">
         <is>
           <t>The event status remains "Confirmed"; the affected venue booking is shown flagged, but no automatic status change has occurred</t>
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="2" t="n">
+    <row r="176">
+      <c r="A176" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
         <is>
           <t>E08-S04</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
+      <c r="C176" s="2" t="inlineStr">
         <is>
           <t>E08-S04 (checklist: reversion recorded in activity log)</t>
         </is>
       </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>3 - Cross-cutting (audit logging)</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>TC_E08S04_04</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>Verify that a reversion from Confirmed to Planning should be recorded in the activity log</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr">
         <is>
           <t>Event "Leadership Summit" has just been reverted from "Confirmed" to "Planning" by coordinator_1@connectsphere.com</t>
         </is>
       </c>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>1. Log in as a System Administrator
   2. Open the Activity Log and search for "Leadership Summit"</t>
         </is>
       </c>
-      <c r="I173" s="2" t="inlineStr">
+      <c r="I176" s="2" t="inlineStr">
         <is>
           <t>Event: Leadership Summit</t>
         </is>
       </c>
-      <c r="J173" s="2" t="inlineStr">
+      <c r="J176" s="2" t="inlineStr">
         <is>
           <t>An activity log entry exists recording the reversion, with actor = coordinator_1@connectsphere.com, action = "Reverted to Planning", and a timestamp
 ## E08-S05</t>
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="2" t="n">
+    <row r="177">
+      <c r="A177" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B174" s="2" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="C174" s="2" t="inlineStr">
+      <c r="C177" s="2" t="inlineStr">
         <is>
           <t>E08-S05 - Scenario 1 (Auto-completed after the end time)</t>
         </is>
       </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>TC_E08S05_01</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>Verify that a Confirmed event should automatically become Completed once its last event's end time has passed</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr">
         <is>
           <t>Event "Charity Run" has status "Confirmed"; its only event ended at 17:00 on 15/01/2027, which has now passed</t>
         </is>
       </c>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>1. Wait for (or trigger) the system's next scheduled evaluation after 17:00 on 15/01/2027
   2. Open event "Charity Run" and check its status</t>
         </is>
       </c>
-      <c r="I174" s="2" t="inlineStr">
+      <c r="I177" s="2" t="inlineStr">
         <is>
           <t>Event end time: 17:00, 15/01/2027 (passed)</t>
         </is>
       </c>
-      <c r="J174" s="2" t="inlineStr">
+      <c r="J177" s="2" t="inlineStr">
         <is>
           <t>The event status has automatically changed to "Completed"</t>
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="2" t="n">
+    <row r="178">
+      <c r="A178" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
+      <c r="C178" s="2" t="inlineStr">
         <is>
           <t>E08-S05 - Scenario 2 (Marked complete manually)</t>
         </is>
       </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>TC_E08S05_02</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>Verify that an Event Coordinator should be able to manually mark a Confirmed event complete once its last event has started</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr">
         <is>
           <t>Event "Volunteer Training Day" has status "Confirmed"; its last (only) event started at 09:00 today and is still in progress</t>
         </is>
       </c>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Volunteer Training Day"
   3. Click "Mark Complete"</t>
         </is>
       </c>
-      <c r="I175" s="2" t="inlineStr">
+      <c r="I178" s="2" t="inlineStr">
         <is>
           <t>Event started: 09:00 today</t>
         </is>
       </c>
-      <c r="J175" s="2" t="inlineStr">
+      <c r="J178" s="2" t="inlineStr">
         <is>
           <t>The event status changes to "Completed"</t>
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="2" t="n">
+    <row r="179">
+      <c r="A179" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B176" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="C176" s="2" t="inlineStr">
+      <c r="C179" s="2" t="inlineStr">
         <is>
           <t>E08-S05 - Scenario 3 (Premature completion blocked)</t>
         </is>
       </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>TC_E08S05_03</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to mark an event complete before its first event has started should be blocked</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Conference 2026" has status "Confirmed"; its first event has not yet started</t>
         </is>
       </c>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Tech Conference 2026"
   3. Attempt to click "Mark Complete"</t>
         </is>
       </c>
-      <c r="I176" s="2" t="inlineStr">
+      <c r="I179" s="2" t="inlineStr">
         <is>
           <t>First event: not yet started</t>
         </is>
       </c>
-      <c r="J176" s="2" t="inlineStr">
+      <c r="J179" s="2" t="inlineStr">
         <is>
           <t>The action is blocked; the event cannot be marked complete before it has started</t>
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="2" t="n">
+    <row r="180">
+      <c r="A180" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B177" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="C177" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
         <is>
           <t>E08-S05 - Scenario 4 (Cancelled event never auto-completes)</t>
         </is>
       </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>TC_E08S05_04</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>Verify that a Cancelled event should never auto-complete, even after its original end time passes</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr">
         <is>
           <t>Event "Product Launch Night" has status "Cancelled" (per TC_E10S04_01); its original end time has now passed</t>
         </is>
       </c>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>1. Wait for (or trigger) the system's next scheduled evaluation after "Product Launch Night"'s original end time
   2. Open event "Product Launch Night" and check its status</t>
         </is>
       </c>
-      <c r="I177" s="2" t="inlineStr">
+      <c r="I180" s="2" t="inlineStr">
         <is>
           <t>Original end time: passed</t>
         </is>
       </c>
-      <c r="J177" s="2" t="inlineStr">
+      <c r="J180" s="2" t="inlineStr">
         <is>
           <t>The event status remains "Cancelled"; it has not been auto-completed</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="2" t="n">
+    <row r="181">
+      <c r="A181" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B178" s="2" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="C178" s="2" t="inlineStr">
+      <c r="C181" s="2" t="inlineStr">
         <is>
           <t>E08-S05 (checklist: transition to Completed logged)</t>
         </is>
       </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>3 - Cross-cutting (audit logging)</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>TC_E08S05_05</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>Verify that an event's transition to Completed should be recorded in the activity log</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr">
         <is>
           <t>Event "Charity Run" has just transitioned to "Completed" (per TC_E08S05_01)</t>
         </is>
       </c>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t>1. Log in as a System Administrator
   2. Open the Activity Log and search for "Charity Run"</t>
         </is>
       </c>
-      <c r="I178" s="2" t="inlineStr">
+      <c r="I181" s="2" t="inlineStr">
         <is>
           <t>Event: Charity Run</t>
         </is>
       </c>
-      <c r="J178" s="2" t="inlineStr">
+      <c r="J181" s="2" t="inlineStr">
         <is>
           <t>An activity log entry exists recording the transition to "Completed", with the time it occurred</t>
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="2" t="n">
+    <row r="182">
+      <c r="A182" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B179" s="2" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="C179" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
         <is>
           <t>E08-S05 · Scenario 1 (Auto-completed after the end time)</t>
         </is>
       </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (exactly at)</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>TC_E08S05_06</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>Verify that an event auto-completes at the exact end time and not before</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr">
         <is>
           <t>Event EVT-2002 is Confirmed and its end time is 2026-11-02 17:00:00 +08:00</t>
         </is>
       </c>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>1. Set the system clock to 2026-11-02 16:59:59 +08:00 and trigger the completion evaluation
  2. Record the event status
@@ -9837,52 +9999,52 @@
  4. Record the event status</t>
         </is>
       </c>
-      <c r="I179" s="2" t="inlineStr">
+      <c r="I182" s="2" t="inlineStr">
         <is>
           <t>Event ends: 2026-11-02 17:00:00 +08:00 · Evaluations at 16:59:59 and 17:00:00</t>
         </is>
       </c>
-      <c r="J179" s="2" t="inlineStr">
+      <c r="J182" s="2" t="inlineStr">
         <is>
           <t>At 16:59:59 the status remains Confirmed. At 17:00:00 the status becomes Completed and the transition is recorded in the activity log</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="2" t="n">
+    <row r="183">
+      <c r="A183" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B180" s="2" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="C180" s="2" t="inlineStr">
+      <c r="C183" s="2" t="inlineStr">
         <is>
           <t>E09-S01 - Scenario 1 (Place reserved in an open event)</t>
         </is>
       </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>TC_E09S01_01</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>Verify that submitting the required registration information for an open event with places remaining should reserve a place and provide a confirmation</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr">
         <is>
           <t>Event "Community Meetup" is Confirmed, registration is open, and 3 of 5 places remain in its event</t>
         </is>
       </c>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_c@example.com
   2. Open event "Community Meetup"
@@ -9890,52 +10052,52 @@
   4. Submit registration</t>
         </is>
       </c>
-      <c r="I180" s="2" t="inlineStr">
+      <c r="I183" s="2" t="inlineStr">
         <is>
           <t>Name: Casey Tan | Email: attendee_c@example.com</t>
         </is>
       </c>
-      <c r="J180" s="2" t="inlineStr">
+      <c r="J183" s="2" t="inlineStr">
         <is>
           <t>attendee_c@example.com's place is reserved, and they receive a confirmation containing the event's details (date, time, venue)</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="2" t="n">
+    <row r="184">
+      <c r="A184" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B181" s="2" t="inlineStr">
+      <c r="B184" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="C181" s="2" t="inlineStr">
+      <c r="C184" s="2" t="inlineStr">
         <is>
           <t>E09-S01 (checklist: choose events to attend in a multi-event event)</t>
         </is>
       </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>TC_E09S01_02</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>Verify that registering for a multi-event event should let the Attendee choose which events to attend, reserving a place in each chosen event</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Conference 2026" has the event and the event, both open for registration</t>
         </is>
       </c>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_d@example.com
   2. Open event "Tech Conference 2026"
@@ -9943,104 +10105,104 @@
   4. Submit registration</t>
         </is>
       </c>
-      <c r="I181" s="2" t="inlineStr">
+      <c r="I184" s="2" t="inlineStr">
         <is>
           <t>Selected: the event only</t>
         </is>
       </c>
-      <c r="J181" s="2" t="inlineStr">
+      <c r="J184" s="2" t="inlineStr">
         <is>
           <t>A place is reserved for attendee_d@example.com in the event only; they are not registered for the event</t>
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="2" t="n">
+    <row r="185">
+      <c r="A185" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B182" s="2" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="C182" s="2" t="inlineStr">
+      <c r="C185" s="2" t="inlineStr">
         <is>
           <t>E09-S01 - Scenario 2 (Duplicate registration prevented)</t>
         </is>
       </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>TC_E09S01_03</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to register again for a event already registered for should be told so, without creating a duplicate</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr">
         <is>
           <t>attendee_c@example.com is already registered for "Community Meetup"'s event</t>
         </is>
       </c>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="H185" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_c@example.com
   2. Open event "Community Meetup"
   3. Attempt to register again</t>
         </is>
       </c>
-      <c r="I182" s="2" t="inlineStr">
+      <c r="I185" s="2" t="inlineStr">
         <is>
           <t>Attendee: attendee_c@example.com (already registered)</t>
         </is>
       </c>
-      <c r="J182" s="2" t="inlineStr">
+      <c r="J185" s="2" t="inlineStr">
         <is>
           <t>attendee_c@example.com is told they are already registered; no duplicate registration is created</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="2" t="n">
+    <row r="186">
+      <c r="A186" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B183" s="2" t="inlineStr">
+      <c r="B186" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="C183" s="2" t="inlineStr">
+      <c r="C186" s="2" t="inlineStr">
         <is>
           <t>E09-S01 - Scenario 3 (Missing fields identified)</t>
         </is>
       </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>TC_E09S01_04</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F186" s="2" t="inlineStr">
         <is>
           <t>Verify that submitting registration with a required field empty should block registration and identify the missing fields</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr">
+      <c r="G186" s="2" t="inlineStr">
         <is>
           <t>Event "Community Meetup" is open for registration</t>
         </is>
       </c>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="H186" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_e@example.com
   2. Open event "Community Meetup"
@@ -10048,271 +10210,118 @@
   4. Submit registration</t>
         </is>
       </c>
-      <c r="I183" s="2" t="inlineStr">
+      <c r="I186" s="2" t="inlineStr">
         <is>
           <t>Name: filled | Email: (blank)</t>
         </is>
       </c>
-      <c r="J183" s="2" t="inlineStr">
+      <c r="J186" s="2" t="inlineStr">
         <is>
           <t>Registration is blocked, and the Email field is identified as missing</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="2" t="n">
+    <row r="187">
+      <c r="A187" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B184" s="2" t="inlineStr">
+      <c r="B187" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="C184" s="2" t="inlineStr">
+      <c r="C187" s="2" t="inlineStr">
         <is>
           <t>E09-S01 - Scenario 4 (Unconfirmed event refused)</t>
         </is>
       </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="D187" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>TC_E09S01_05</t>
         </is>
       </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="F187" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to register for an event that is not Confirmed should be refused</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr">
+      <c r="G187" s="2" t="inlineStr">
         <is>
           <t>Event "Draft Networking Event" has status "Planning" (not yet Confirmed)</t>
         </is>
       </c>
-      <c r="H184" s="2" t="inlineStr">
+      <c r="H187" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_c@example.com
   2. Attempt to open the registration form for "Draft Networking Event"</t>
         </is>
       </c>
-      <c r="I184" s="2" t="inlineStr">
+      <c r="I187" s="2" t="inlineStr">
         <is>
           <t>Event status: Planning</t>
         </is>
       </c>
-      <c r="J184" s="2" t="inlineStr">
+      <c r="J187" s="2" t="inlineStr">
         <is>
           <t>Registration is refused, since the event is not yet Confirmed
 ## E09-S02</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="2" t="n">
+    <row r="188">
+      <c r="A188" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B185" s="2" t="inlineStr">
+      <c r="B188" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="C185" s="2" t="inlineStr">
+      <c r="C188" s="2" t="inlineStr">
         <is>
           <t>E09-S02 (checklist: set a registration limit)</t>
         </is>
       </c>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="D188" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E188" s="2" t="inlineStr">
         <is>
           <t>TC_E09S02_01</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="F188" s="2" t="inlineStr">
         <is>
           <t>Verify that an Event Organiser should be able to set a registration limit for a event</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr">
+      <c r="G188" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com is signed in; event "Community Meetup"'s event has no registration limit set yet</t>
         </is>
       </c>
-      <c r="H185" s="2" t="inlineStr">
+      <c r="H188" s="2" t="inlineStr">
         <is>
           <t>1. Open event "Community Meetup"
   2. Set the Registration Limit for its event to 5
   3. Save</t>
         </is>
       </c>
-      <c r="I185" s="2" t="inlineStr">
+      <c r="I188" s="2" t="inlineStr">
         <is>
           <t>Registration Limit: 5</t>
         </is>
       </c>
-      <c r="J185" s="2" t="inlineStr">
+      <c r="J188" s="2" t="inlineStr">
         <is>
           <t>The event's registration limit is saved as 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B186" s="2" t="inlineStr">
-        <is>
-          <t>E09-S02</t>
-        </is>
-      </c>
-      <c r="C186" s="2" t="inlineStr">
-        <is>
-          <t>E09-S02 - Scenario 1 (Venue capacity enforced)</t>
-        </is>
-      </c>
-      <c r="D186" s="2" t="inlineStr">
-        <is>
-          <t>5 - Boundary (exactly at)</t>
-        </is>
-      </c>
-      <c r="E186" s="2" t="inlineStr">
-        <is>
-          <t>TC_E09S02_02</t>
-        </is>
-      </c>
-      <c r="F186" s="2" t="inlineStr">
-        <is>
-          <t>Verify that registration should stop once the event reaches the lower of the Organiser's limit and the booked venue's capacity</t>
-        </is>
-      </c>
-      <c r="G186" s="2" t="inlineStr">
-        <is>
-          <t>"Community Meetup"'s event has an Organiser-set limit of 5 and a booked venue capacity of 8 (the limit is the lower value); 5 Attendees are already registered</t>
-        </is>
-      </c>
-      <c r="H186" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in as attendee_f@example.com
-  2. Attempt to register for "Community Meetup"</t>
-        </is>
-      </c>
-      <c r="I186" s="2" t="inlineStr">
-        <is>
-          <t>Registered so far: 5 (effective limit) | Venue capacity: 8</t>
-        </is>
-      </c>
-      <c r="J186" s="2" t="inlineStr">
-        <is>
-          <t>Registration is refused since the event has reached its effective capacity of 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B187" s="2" t="inlineStr">
-        <is>
-          <t>E09-S02</t>
-        </is>
-      </c>
-      <c r="C187" s="2" t="inlineStr">
-        <is>
-          <t>E09-S02 - Scenario 2 (Simultaneous final registration)</t>
-        </is>
-      </c>
-      <c r="D187" s="2" t="inlineStr">
-        <is>
-          <t>5 - Boundary (last place, concurrency)</t>
-        </is>
-      </c>
-      <c r="E187" s="2" t="inlineStr">
-        <is>
-          <t>TC_E09S02_03</t>
-        </is>
-      </c>
-      <c r="F187" s="2" t="inlineStr">
-        <is>
-          <t>Verify that when only one place remains, two simultaneous registration attempts should result in exactly one success</t>
-        </is>
-      </c>
-      <c r="G187" s="2" t="inlineStr">
-        <is>
-          <t>"Community Meetup"'s event has exactly 1 place remaining</t>
-        </is>
-      </c>
-      <c r="H187" s="2" t="inlineStr">
-        <is>
-          <t>1. Have attendee_g@example.com and attendee_h@example.com submit registration for the same event at the same moment
-  2. Check both outcomes</t>
-        </is>
-      </c>
-      <c r="I187" s="2" t="inlineStr">
-        <is>
-          <t>1 place remaining | 2 simultaneous attempts</t>
-        </is>
-      </c>
-      <c r="J187" s="2" t="inlineStr">
-        <is>
-          <t>Exactly one of the two registrations succeeds; the other is told the event is full</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B188" s="2" t="inlineStr">
-        <is>
-          <t>E09-S02</t>
-        </is>
-      </c>
-      <c r="C188" s="2" t="inlineStr">
-        <is>
-          <t>E09-S02 - Scenario 3 (Full event offers the waiting list)</t>
-        </is>
-      </c>
-      <c r="D188" s="2" t="inlineStr">
-        <is>
-          <t>2 - Happy Path</t>
-        </is>
-      </c>
-      <c r="E188" s="2" t="inlineStr">
-        <is>
-          <t>TC_E09S02_04</t>
-        </is>
-      </c>
-      <c r="F188" s="2" t="inlineStr">
-        <is>
-          <t>Verify that opening the registration page for a full event should close registration and offer the waiting list where enabled</t>
-        </is>
-      </c>
-      <c r="G188" s="2" t="inlineStr">
-        <is>
-          <t>"Community Meetup"'s event is full (5 of 5 places taken); the waiting list is enabled for this event</t>
-        </is>
-      </c>
-      <c r="H188" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in as attendee_i@example.com
-  2. Open the registration page for "Community Meetup"</t>
-        </is>
-      </c>
-      <c r="I188" s="2" t="inlineStr">
-        <is>
-          <t>Event: full | Waiting list: enabled</t>
-        </is>
-      </c>
-      <c r="J188" s="2" t="inlineStr">
-        <is>
-          <t>Registration is shown as closed, and the option to join the waiting list is offered</t>
         </is>
       </c>
     </row>
@@ -10327,30 +10336,183 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
+          <t>E09-S02 - Scenario 1 (Venue capacity enforced)</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>5 - Boundary (exactly at)</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>TC_E09S02_02</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>Verify that registration should stop once the event reaches the lower of the Organiser's limit and the booked venue's capacity</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>"Community Meetup"'s event has an Organiser-set limit of 5 and a booked venue capacity of 8 (the limit is the lower value); 5 Attendees are already registered</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in as attendee_f@example.com
+  2. Attempt to register for "Community Meetup"</t>
+        </is>
+      </c>
+      <c r="I189" s="2" t="inlineStr">
+        <is>
+          <t>Registered so far: 5 (effective limit) | Venue capacity: 8</t>
+        </is>
+      </c>
+      <c r="J189" s="2" t="inlineStr">
+        <is>
+          <t>Registration is refused since the event has reached its effective capacity of 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>E09-S02</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>E09-S02 - Scenario 2 (Simultaneous final registration)</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>5 - Boundary (last place, concurrency)</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>TC_E09S02_03</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>Verify that when only one place remains, two simultaneous registration attempts should result in exactly one success</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>"Community Meetup"'s event has exactly 1 place remaining</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>1. Have attendee_g@example.com and attendee_h@example.com submit registration for the same event at the same moment
+  2. Check both outcomes</t>
+        </is>
+      </c>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t>1 place remaining | 2 simultaneous attempts</t>
+        </is>
+      </c>
+      <c r="J190" s="2" t="inlineStr">
+        <is>
+          <t>Exactly one of the two registrations succeeds; the other is told the event is full</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>E09-S02</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>E09-S02 - Scenario 3 (Full event offers the waiting list)</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>2 - Happy Path</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>TC_E09S02_04</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>Verify that opening the registration page for a full event should close registration and offer the waiting list where enabled</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>"Community Meetup"'s event is full (5 of 5 places taken); the waiting list is enabled for this event</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in as attendee_i@example.com
+  2. Open the registration page for "Community Meetup"</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>Event: full | Waiting list: enabled</t>
+        </is>
+      </c>
+      <c r="J191" s="2" t="inlineStr">
+        <is>
+          <t>Registration is shown as closed, and the option to join the waiting list is offered</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>E09-S02</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
           <t>E09-S02 · Scenario 4 (VIP added beyond normal registration)</t>
         </is>
       </c>
-      <c r="D189" s="2" t="inlineStr">
+      <c r="D192" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (just below venue capacity)</t>
         </is>
       </c>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="E192" s="2" t="inlineStr">
         <is>
           <t>TC_E09S02_06</t>
         </is>
       </c>
-      <c r="F189" s="2" t="inlineStr">
+      <c r="F192" s="2" t="inlineStr">
         <is>
           <t>Verify that a VIP can be added manually when normal registration is full but venue capacity is not reached</t>
         </is>
       </c>
-      <c r="G189" s="2" t="inlineStr">
+      <c r="G192" s="2" t="inlineStr">
         <is>
           <t>Event EVT-2001 is Confirmed with Orchid Hall booked, venue capacity 200. Normal registration has closed at 199 registrations. Coordinator coord_a@connectsphere.com is signed in</t>
         </is>
       </c>
-      <c r="H189" s="2" t="inlineStr">
+      <c r="H192" s="2" t="inlineStr">
         <is>
           <t>1. Open event EVT-2001
  2. Select Add attendee manually
@@ -10358,52 +10520,52 @@
  4. Confirm the addition</t>
         </is>
       </c>
-      <c r="I189" s="2" t="inlineStr">
+      <c r="I192" s="2" t="inlineStr">
         <is>
           <t>Venue capacity: 200 · Current registrations: 199 · Added: 1</t>
         </is>
       </c>
-      <c r="J189" s="2" t="inlineStr">
+      <c r="J192" s="2" t="inlineStr">
         <is>
           <t>The registration is created, total registrations reach 200, and the record is marked as a manual addition distinguishable from a normal registration</t>
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="2" t="n">
+    <row r="193">
+      <c r="A193" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B190" s="2" t="inlineStr">
+      <c r="B193" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="C190" s="2" t="inlineStr">
+      <c r="C193" s="2" t="inlineStr">
         <is>
           <t>E09-S02 · Scenario 5 (VIP blocked at venue capacity)</t>
         </is>
       </c>
-      <c r="D190" s="2" t="inlineStr">
+      <c r="D193" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (exactly at venue capacity)</t>
         </is>
       </c>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="E193" s="2" t="inlineStr">
         <is>
           <t>TC_E09S02_07</t>
         </is>
       </c>
-      <c r="F190" s="2" t="inlineStr">
+      <c r="F193" s="2" t="inlineStr">
         <is>
           <t>Verify that a manual VIP addition is blocked once total registrations equal venue capacity</t>
         </is>
       </c>
-      <c r="G190" s="2" t="inlineStr">
+      <c r="G193" s="2" t="inlineStr">
         <is>
           <t>Event EVT-2001 is Confirmed with Orchid Hall booked, venue capacity 200, and 200 registrations already recorded. Coordinator coord_a@connectsphere.com is signed in</t>
         </is>
       </c>
-      <c r="H190" s="2" t="inlineStr">
+      <c r="H193" s="2" t="inlineStr">
         <is>
           <t>1. Open event EVT-2001
  2. Select Add attendee manually
@@ -10411,272 +10573,119 @@
  4. Confirm the addition</t>
         </is>
       </c>
-      <c r="I190" s="2" t="inlineStr">
+      <c r="I193" s="2" t="inlineStr">
         <is>
           <t>Venue capacity: 200 · Current registrations: 200</t>
         </is>
       </c>
-      <c r="J190" s="2" t="inlineStr">
+      <c r="J193" s="2" t="inlineStr">
         <is>
           <t>The addition is blocked with a message stating the booked venue capacity has been reached. No registration is created
 ## E09-S03</t>
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="2" t="n">
+    <row r="194">
+      <c r="A194" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B191" s="2" t="inlineStr">
+      <c r="B194" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="C191" s="2" t="inlineStr">
+      <c r="C194" s="2" t="inlineStr">
         <is>
           <t>E09-S03 (checklist: set registration opening/closing dates)</t>
         </is>
       </c>
-      <c r="D191" s="2" t="inlineStr">
+      <c r="D194" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E191" s="2" t="inlineStr">
+      <c r="E194" s="2" t="inlineStr">
         <is>
           <t>TC_E09S03_01</t>
         </is>
       </c>
-      <c r="F191" s="2" t="inlineStr">
+      <c r="F194" s="2" t="inlineStr">
         <is>
           <t>Verify that an Event Organiser should be able to set the registration opening and closing dates for an event</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr">
+      <c r="G194" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com is signed in; event "Community Meetup" has no registration dates set</t>
         </is>
       </c>
-      <c r="H191" s="2" t="inlineStr">
+      <c r="H194" s="2" t="inlineStr">
         <is>
           <t>1. Open event "Community Meetup"
   2. Set Registration Opens: 01/10/2026, Registration Closes: 01/12/2026
   3. Save</t>
         </is>
       </c>
-      <c r="I191" s="2" t="inlineStr">
+      <c r="I194" s="2" t="inlineStr">
         <is>
           <t>Opens: 01/10/2026 | Closes: 01/12/2026</t>
         </is>
       </c>
-      <c r="J191" s="2" t="inlineStr">
+      <c r="J194" s="2" t="inlineStr">
         <is>
           <t>The registration opening and closing dates are saved as entered</t>
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="2" t="n">
+    <row r="195">
+      <c r="A195" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B192" s="2" t="inlineStr">
+      <c r="B195" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="C192" s="2" t="inlineStr">
+      <c r="C195" s="2" t="inlineStr">
         <is>
           <t>E09-S03 (checklist: set a withdrawal deadline)</t>
         </is>
       </c>
-      <c r="D192" s="2" t="inlineStr">
+      <c r="D195" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="E195" s="2" t="inlineStr">
         <is>
           <t>TC_E09S03_02</t>
         </is>
       </c>
-      <c r="F192" s="2" t="inlineStr">
+      <c r="F195" s="2" t="inlineStr">
         <is>
           <t>Verify that an Event Organiser should be able to set a withdrawal deadline for an event</t>
         </is>
       </c>
-      <c r="G192" s="2" t="inlineStr">
+      <c r="G195" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com is signed in; event "Community Meetup" has no withdrawal deadline set</t>
         </is>
       </c>
-      <c r="H192" s="2" t="inlineStr">
+      <c r="H195" s="2" t="inlineStr">
         <is>
           <t>1. Open event "Community Meetup"
   2. Set Withdrawal Deadline: 10/12/2026
   3. Save</t>
         </is>
       </c>
-      <c r="I192" s="2" t="inlineStr">
+      <c r="I195" s="2" t="inlineStr">
         <is>
           <t>Withdrawal Deadline: 10/12/2026</t>
         </is>
       </c>
-      <c r="J192" s="2" t="inlineStr">
+      <c r="J195" s="2" t="inlineStr">
         <is>
           <t>The withdrawal deadline is saved as 10/12/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B193" s="2" t="inlineStr">
-        <is>
-          <t>E09-S03</t>
-        </is>
-      </c>
-      <c r="C193" s="2" t="inlineStr">
-        <is>
-          <t>E09-S03 - Scenario 1 (Before registration opens)</t>
-        </is>
-      </c>
-      <c r="D193" s="2" t="inlineStr">
-        <is>
-          <t>5 - Boundary (before)</t>
-        </is>
-      </c>
-      <c r="E193" s="2" t="inlineStr">
-        <is>
-          <t>TC_E09S03_03</t>
-        </is>
-      </c>
-      <c r="F193" s="2" t="inlineStr">
-        <is>
-          <t>Verify that an Attendee viewing an event before its registration opening date should see registration as not yet open, with the opening date stated</t>
-        </is>
-      </c>
-      <c r="G193" s="2" t="inlineStr">
-        <is>
-          <t>"Community Meetup"'s registration opening date (01/10/2026) has not yet been reached</t>
-        </is>
-      </c>
-      <c r="H193" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in as attendee_c@example.com
-  2. Open event "Community Meetup"</t>
-        </is>
-      </c>
-      <c r="I193" s="2" t="inlineStr">
-        <is>
-          <t>Opening date: 01/10/2026 (not reached)</t>
-        </is>
-      </c>
-      <c r="J193" s="2" t="inlineStr">
-        <is>
-          <t>Registration is shown as "Not yet open", with the message stating it opens on 01/10/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B194" s="2" t="inlineStr">
-        <is>
-          <t>E09-S03</t>
-        </is>
-      </c>
-      <c r="C194" s="2" t="inlineStr">
-        <is>
-          <t>E09-S03 - Scenario 2 (After registration closes)</t>
-        </is>
-      </c>
-      <c r="D194" s="2" t="inlineStr">
-        <is>
-          <t>5 - Boundary (after)</t>
-        </is>
-      </c>
-      <c r="E194" s="2" t="inlineStr">
-        <is>
-          <t>TC_E09S03_04</t>
-        </is>
-      </c>
-      <c r="F194" s="2" t="inlineStr">
-        <is>
-          <t>Verify that an Attendee trying to register after the registration closing date has passed should be refused</t>
-        </is>
-      </c>
-      <c r="G194" s="2" t="inlineStr">
-        <is>
-          <t>"Community Meetup"'s registration closing date (01/12/2026) has passed</t>
-        </is>
-      </c>
-      <c r="H194" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in as attendee_c@example.com
-  2. Attempt to register for "Community Meetup"</t>
-        </is>
-      </c>
-      <c r="I194" s="2" t="inlineStr">
-        <is>
-          <t>Closing date: 01/12/2026 (passed)</t>
-        </is>
-      </c>
-      <c r="J194" s="2" t="inlineStr">
-        <is>
-          <t>Registration is refused, since the closing date has passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B195" s="2" t="inlineStr">
-        <is>
-          <t>E09-S03</t>
-        </is>
-      </c>
-      <c r="C195" s="2" t="inlineStr">
-        <is>
-          <t>E09-S03 - Scenario 3 (Closing date after event start warned)</t>
-        </is>
-      </c>
-      <c r="D195" s="2" t="inlineStr">
-        <is>
-          <t>4 - Negative</t>
-        </is>
-      </c>
-      <c r="E195" s="2" t="inlineStr">
-        <is>
-          <t>TC_E09S03_05</t>
-        </is>
-      </c>
-      <c r="F195" s="2" t="inlineStr">
-        <is>
-          <t>Verify that setting a registration closing date that falls after the event has started should warn the Organiser and ask them to confirm</t>
-        </is>
-      </c>
-      <c r="G195" s="2" t="inlineStr">
-        <is>
-          <t>organiser_a@clienta.com is editing event "Community Meetup", which starts on 15/11/2026</t>
-        </is>
-      </c>
-      <c r="H195" s="2" t="inlineStr">
-        <is>
-          <t>1. Set Registration Closes: 20/11/2026 (after the event's start date)
-  2. Click "Save"</t>
-        </is>
-      </c>
-      <c r="I195" s="2" t="inlineStr">
-        <is>
-          <t>Closing date: 20/11/2026 (after event start 15/11/2026)</t>
-        </is>
-      </c>
-      <c r="J195" s="2" t="inlineStr">
-        <is>
-          <t>A warning is shown asking the Organiser to confirm this is intended, before the closing date is saved</t>
         </is>
       </c>
     </row>
@@ -10691,30 +10700,183 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
+          <t>E09-S03 - Scenario 1 (Before registration opens)</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>5 - Boundary (before)</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>TC_E09S03_03</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>Verify that an Attendee viewing an event before its registration opening date should see registration as not yet open, with the opening date stated</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>"Community Meetup"'s registration opening date (01/10/2026) has not yet been reached</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in as attendee_c@example.com
+  2. Open event "Community Meetup"</t>
+        </is>
+      </c>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>Opening date: 01/10/2026 (not reached)</t>
+        </is>
+      </c>
+      <c r="J196" s="2" t="inlineStr">
+        <is>
+          <t>Registration is shown as "Not yet open", with the message stating it opens on 01/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>E09-S03</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>E09-S03 - Scenario 2 (After registration closes)</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>5 - Boundary (after)</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>TC_E09S03_04</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>Verify that an Attendee trying to register after the registration closing date has passed should be refused</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>"Community Meetup"'s registration closing date (01/12/2026) has passed</t>
+        </is>
+      </c>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in as attendee_c@example.com
+  2. Attempt to register for "Community Meetup"</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t>Closing date: 01/12/2026 (passed)</t>
+        </is>
+      </c>
+      <c r="J197" s="2" t="inlineStr">
+        <is>
+          <t>Registration is refused, since the closing date has passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>E09-S03</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>E09-S03 - Scenario 3 (Closing date after event start warned)</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>4 - Negative</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>TC_E09S03_05</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>Verify that setting a registration closing date that falls after the event has started should warn the Organiser and ask them to confirm</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>organiser_a@clienta.com is editing event "Community Meetup", which starts on 15/11/2026</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>1. Set Registration Closes: 20/11/2026 (after the event's start date)
+  2. Click "Save"</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>Closing date: 20/11/2026 (after event start 15/11/2026)</t>
+        </is>
+      </c>
+      <c r="J198" s="2" t="inlineStr">
+        <is>
+          <t>A warning is shown asking the Organiser to confirm this is intended, before the closing date is saved</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>E09-S03</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
           <t>E09-S03 - Scenario 4 (Waiting list enabled)</t>
         </is>
       </c>
-      <c r="D196" s="2" t="inlineStr">
+      <c r="D199" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E196" s="2" t="inlineStr">
+      <c r="E199" s="2" t="inlineStr">
         <is>
           <t>TC_E09S03_06</t>
         </is>
       </c>
-      <c r="F196" s="2" t="inlineStr">
+      <c r="F199" s="2" t="inlineStr">
         <is>
           <t>Verify that enabling the waiting list for an event should offer it to Attendees once a event becomes full</t>
         </is>
       </c>
-      <c r="G196" s="2" t="inlineStr">
+      <c r="G199" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com is about to enable the waiting list for event "Community Meetup"</t>
         </is>
       </c>
-      <c r="H196" s="2" t="inlineStr">
+      <c r="H199" s="2" t="inlineStr">
         <is>
           <t>1. Open event "Community Meetup"
   2. Toggle "Enable Waiting List" on
@@ -10722,363 +10884,363 @@
   4. Fill the event to capacity and attempt a further registration</t>
         </is>
       </c>
-      <c r="I196" s="2" t="inlineStr">
+      <c r="I199" s="2" t="inlineStr">
         <is>
           <t>Waiting List: Enabled</t>
         </is>
       </c>
-      <c r="J196" s="2" t="inlineStr">
+      <c r="J199" s="2" t="inlineStr">
         <is>
           <t>Once the event is full, the further registration attempt is offered the waiting list instead of being simply refused</t>
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="2" t="n">
+    <row r="200">
+      <c r="A200" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B197" s="2" t="inlineStr">
+      <c r="B200" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="C197" s="2" t="inlineStr">
+      <c r="C200" s="2" t="inlineStr">
         <is>
           <t>E09-S03 · Scenario 1 (Before registration opens)</t>
         </is>
       </c>
-      <c r="D197" s="2" t="inlineStr">
+      <c r="D200" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (exactly at)</t>
         </is>
       </c>
-      <c r="E197" s="2" t="inlineStr">
+      <c r="E200" s="2" t="inlineStr">
         <is>
           <t>TC_E09S03_07</t>
         </is>
       </c>
-      <c r="F197" s="2" t="inlineStr">
+      <c r="F200" s="2" t="inlineStr">
         <is>
           <t>Verify that registration succeeds at the exact opening timestamp</t>
         </is>
       </c>
-      <c r="G197" s="2" t="inlineStr">
+      <c r="G200" s="2" t="inlineStr">
         <is>
           <t>Event EVT-2001 is Confirmed with registration opening at 2026-10-01 09:00:00 +08:00. Attendee attendee_a@example.com is signed in. Event EVT-2001 has places remaining</t>
         </is>
       </c>
-      <c r="H197" s="2" t="inlineStr">
+      <c r="H200" s="2" t="inlineStr">
         <is>
           <t>1. Set the system clock to exactly 2026-10-01 09:00:00 +08:00
  2. Open event EVT-2001
  3. Select event EVT-2001 and submit registration</t>
         </is>
       </c>
-      <c r="I197" s="2" t="inlineStr">
+      <c r="I200" s="2" t="inlineStr">
         <is>
           <t>Registration opens: 2026-10-01 09:00:00 +08:00 · Attempt at: 2026-10-01 09:00:00 +08:00</t>
         </is>
       </c>
-      <c r="J197" s="2" t="inlineStr">
+      <c r="J200" s="2" t="inlineStr">
         <is>
           <t>Registration succeeds and a place is reserved. The opening moment is inclusive: registration is open at, not after, the opening timestamp</t>
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" s="2" t="n">
+    <row r="201">
+      <c r="A201" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B198" s="2" t="inlineStr">
+      <c r="B201" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="C198" s="2" t="inlineStr">
+      <c r="C201" s="2" t="inlineStr">
         <is>
           <t>E09-S03 · Scenario 2 (After registration closes)</t>
         </is>
       </c>
-      <c r="D198" s="2" t="inlineStr">
+      <c r="D201" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (exactly at)</t>
         </is>
       </c>
-      <c r="E198" s="2" t="inlineStr">
+      <c r="E201" s="2" t="inlineStr">
         <is>
           <t>TC_E09S03_08</t>
         </is>
       </c>
-      <c r="F198" s="2" t="inlineStr">
+      <c r="F201" s="2" t="inlineStr">
         <is>
           <t>Verify that registration still succeeds at the exact closing timestamp</t>
         </is>
       </c>
-      <c r="G198" s="2" t="inlineStr">
+      <c r="G201" s="2" t="inlineStr">
         <is>
           <t>Event EVT-2001 is Confirmed with registration closing at 2026-10-20 17:00:00 +08:00. Attendee attendee_b@example.com is signed in. Event EVT-2001 has places remaining</t>
         </is>
       </c>
-      <c r="H198" s="2" t="inlineStr">
+      <c r="H201" s="2" t="inlineStr">
         <is>
           <t>1. Set the system clock to exactly 2026-10-20 17:00:00 +08:00
  2. Open event EVT-2001
  3. Select event EVT-2001 and submit registration</t>
         </is>
       </c>
-      <c r="I198" s="2" t="inlineStr">
+      <c r="I201" s="2" t="inlineStr">
         <is>
           <t>Registration closes: 2026-10-20 17:00:00 +08:00 · Attempt at: 2026-10-20 17:00:00 +08:00</t>
         </is>
       </c>
-      <c r="J198" s="2" t="inlineStr">
+      <c r="J201" s="2" t="inlineStr">
         <is>
           <t>Registration succeeds. The acceptance criterion refuses registration once the closing date "has passed", so at the exact closing instant it has not yet passed. One second later the same attempt must be refused
 ## E09-S04</t>
         </is>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" s="2" t="n">
+    <row r="202">
+      <c r="A202" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B199" s="2" t="inlineStr">
+      <c r="B202" s="2" t="inlineStr">
         <is>
           <t>E09-S04</t>
         </is>
       </c>
-      <c r="C199" s="2" t="inlineStr">
+      <c r="C202" s="2" t="inlineStr">
         <is>
           <t>E09-S04 - Scenario 1 (Joined a full event's list)</t>
         </is>
       </c>
-      <c r="D199" s="2" t="inlineStr">
+      <c r="D202" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E199" s="2" t="inlineStr">
+      <c r="E202" s="2" t="inlineStr">
         <is>
           <t>TC_E09S04_01</t>
         </is>
       </c>
-      <c r="F199" s="2" t="inlineStr">
+      <c r="F202" s="2" t="inlineStr">
         <is>
           <t>Verify that joining the waiting list for a full event with the list enabled should add the Attendee and confirm their position</t>
         </is>
       </c>
-      <c r="G199" s="2" t="inlineStr">
+      <c r="G202" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s event is full; the waiting list is enabled and currently empty</t>
         </is>
       </c>
-      <c r="H199" s="2" t="inlineStr">
+      <c r="H202" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_i@example.com
   2. Open the registration page for "Community Meetup"
   3. Click "Join Waiting List"</t>
         </is>
       </c>
-      <c r="I199" s="2" t="inlineStr">
+      <c r="I202" s="2" t="inlineStr">
         <is>
           <t>Waiting list: enabled, currently empty</t>
         </is>
       </c>
-      <c r="J199" s="2" t="inlineStr">
+      <c r="J202" s="2" t="inlineStr">
         <is>
           <t>attendee_i@example.com is added to the waiting list and shown their position (e.g. "Position 1")</t>
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="2" t="n">
+    <row r="203">
+      <c r="A203" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B200" s="2" t="inlineStr">
+      <c r="B203" s="2" t="inlineStr">
         <is>
           <t>E09-S04</t>
         </is>
       </c>
-      <c r="C200" s="2" t="inlineStr">
+      <c r="C203" s="2" t="inlineStr">
         <is>
           <t>E09-S04 - Scenario 2 (Released place notified to all)</t>
         </is>
       </c>
-      <c r="D200" s="2" t="inlineStr">
+      <c r="D203" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E200" s="2" t="inlineStr">
+      <c r="E203" s="2" t="inlineStr">
         <is>
           <t>TC_E09S04_02</t>
         </is>
       </c>
-      <c r="F200" s="2" t="inlineStr">
+      <c r="F203" s="2" t="inlineStr">
         <is>
           <t>Verify that when a place is released in a event with a waiting list, all waitlisted Attendees should be notified and the place claimed on a first-come, first-served basis</t>
         </is>
       </c>
-      <c r="G200" s="2" t="inlineStr">
+      <c r="G203" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s waiting list has attendee_i@example.com (position 1) and attendee_j@example.com (position 2)</t>
         </is>
       </c>
-      <c r="H200" s="2" t="inlineStr">
+      <c r="H203" s="2" t="inlineStr">
         <is>
           <t>1. Have registered Attendee attendee_m@example.com withdraw from "Community Meetup", releasing one place
   2. Check notifications for attendee_i@example.com and attendee_j@example.com
   3. Have attendee_i@example.com claim the released place first</t>
         </is>
       </c>
-      <c r="I200" s="2" t="inlineStr">
+      <c r="I203" s="2" t="inlineStr">
         <is>
           <t>Waiting list: attendee_i@example.com (1st), attendee_j@example.com (2nd)</t>
         </is>
       </c>
-      <c r="J200" s="2" t="inlineStr">
+      <c r="J203" s="2" t="inlineStr">
         <is>
           <t>Both waitlisted Attendees are notified of the released place; attendee_i@example.com successfully claims it since they acted first</t>
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="2" t="n">
+    <row r="204">
+      <c r="A204" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B201" s="2" t="inlineStr">
+      <c r="B204" s="2" t="inlineStr">
         <is>
           <t>E09-S04</t>
         </is>
       </c>
-      <c r="C201" s="2" t="inlineStr">
+      <c r="C204" s="2" t="inlineStr">
         <is>
           <t>E09-S04 - Scenario 3 (Claimed place leaves the list)</t>
         </is>
       </c>
-      <c r="D201" s="2" t="inlineStr">
+      <c r="D204" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E201" s="2" t="inlineStr">
+      <c r="E204" s="2" t="inlineStr">
         <is>
           <t>TC_E09S04_03</t>
         </is>
       </c>
-      <c r="F201" s="2" t="inlineStr">
+      <c r="F204" s="2" t="inlineStr">
         <is>
           <t>Verify that claiming a released place should remove the Attendee from the waiting list for that event</t>
         </is>
       </c>
-      <c r="G201" s="2" t="inlineStr">
+      <c r="G204" s="2" t="inlineStr">
         <is>
           <t>attendee_i@example.com has just claimed a released place in "Community Meetup"'s event</t>
         </is>
       </c>
-      <c r="H201" s="2" t="inlineStr">
+      <c r="H204" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_i@example.com
   2. Check the waiting list for "Community Meetup"'s event</t>
         </is>
       </c>
-      <c r="I201" s="2" t="inlineStr">
+      <c r="I204" s="2" t="inlineStr">
         <is>
           <t>Attendee: attendee_i@example.com (just claimed a place)</t>
         </is>
       </c>
-      <c r="J201" s="2" t="inlineStr">
+      <c r="J204" s="2" t="inlineStr">
         <is>
           <t>attendee_i@example.com no longer appears on the waiting list for that event, since they are now registered</t>
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="2" t="n">
+    <row r="205">
+      <c r="A205" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B202" s="2" t="inlineStr">
+      <c r="B205" s="2" t="inlineStr">
         <is>
           <t>E09-S04</t>
         </is>
       </c>
-      <c r="C202" s="2" t="inlineStr">
+      <c r="C205" s="2" t="inlineStr">
         <is>
           <t>E09-S04 - Scenario 4 (Disabled list offers nothing)</t>
         </is>
       </c>
-      <c r="D202" s="2" t="inlineStr">
+      <c r="D205" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E202" s="2" t="inlineStr">
+      <c r="E205" s="2" t="inlineStr">
         <is>
           <t>TC_E09S04_04</t>
         </is>
       </c>
-      <c r="F202" s="2" t="inlineStr">
+      <c r="F205" s="2" t="inlineStr">
         <is>
           <t>Verify that a full event should not offer a waiting list when the Organiser has disabled it</t>
         </is>
       </c>
-      <c r="G202" s="2" t="inlineStr">
+      <c r="G205" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Conference 2026" has the waiting list disabled; the event is full</t>
         </is>
       </c>
-      <c r="H202" s="2" t="inlineStr">
+      <c r="H205" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_k@example.com
   2. Open the registration page for the event of "Tech Conference 2026"</t>
         </is>
       </c>
-      <c r="I202" s="2" t="inlineStr">
+      <c r="I205" s="2" t="inlineStr">
         <is>
           <t>Waiting list: disabled | the event: full</t>
         </is>
       </c>
-      <c r="J202" s="2" t="inlineStr">
+      <c r="J205" s="2" t="inlineStr">
         <is>
           <t>No waiting list option is offered; registration is simply shown as closed</t>
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="2" t="n">
+    <row r="206">
+      <c r="A206" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B203" s="2" t="inlineStr">
+      <c r="B206" s="2" t="inlineStr">
         <is>
           <t>E09-S04</t>
         </is>
       </c>
-      <c r="C203" s="2" t="inlineStr">
+      <c r="C206" s="2" t="inlineStr">
         <is>
           <t>E09-S04 (checklist: leave the waiting list)</t>
         </is>
       </c>
-      <c r="D203" s="2" t="inlineStr">
+      <c r="D206" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E203" s="2" t="inlineStr">
+      <c r="E206" s="2" t="inlineStr">
         <is>
           <t>TC_E09S04_05</t>
         </is>
       </c>
-      <c r="F203" s="2" t="inlineStr">
+      <c r="F206" s="2" t="inlineStr">
         <is>
           <t>Verify that an Attendee should be able to voluntarily leave the waiting list before a place is released</t>
         </is>
       </c>
-      <c r="G203" s="2" t="inlineStr">
+      <c r="G206" s="2" t="inlineStr">
         <is>
           <t>attendee_j@example.com is on the waiting list for "Community Meetup"'s event, position 2</t>
         </is>
       </c>
-      <c r="H203" s="2" t="inlineStr">
+      <c r="H206" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_j@example.com
   2. Open the waiting list status for "Community Meetup"
@@ -11086,533 +11248,380 @@
   4. Confirm</t>
         </is>
       </c>
-      <c r="I203" s="2" t="inlineStr">
+      <c r="I206" s="2" t="inlineStr">
         <is>
           <t>Attendee: attendee_j@example.com</t>
         </is>
       </c>
-      <c r="J203" s="2" t="inlineStr">
+      <c r="J206" s="2" t="inlineStr">
         <is>
           <t>attendee_j@example.com is removed from the waiting list and no longer receives notifications about released places for that event
 ## E09-S05</t>
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="2" t="n">
+    <row r="207">
+      <c r="A207" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B204" s="2" t="inlineStr">
+      <c r="B207" s="2" t="inlineStr">
         <is>
           <t>E09-S05</t>
         </is>
       </c>
-      <c r="C204" s="2" t="inlineStr">
+      <c r="C207" s="2" t="inlineStr">
         <is>
           <t>E09-S05 - Scenario 1 (Registration withdrawn)</t>
         </is>
       </c>
-      <c r="D204" s="2" t="inlineStr">
+      <c r="D207" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E204" s="2" t="inlineStr">
+      <c r="E207" s="2" t="inlineStr">
         <is>
           <t>TC_E09S05_01</t>
         </is>
       </c>
-      <c r="F204" s="2" t="inlineStr">
+      <c r="F207" s="2" t="inlineStr">
         <is>
           <t>Verify that withdrawing from a single event before the withdrawal deadline should cancel that registration and release the place, leaving other events unaffected</t>
         </is>
       </c>
-      <c r="G204" s="2" t="inlineStr">
+      <c r="G207" s="2" t="inlineStr">
         <is>
           <t>attendee_d@example.com is registered for both the event and the event of "Tech Conference 2026"; the withdrawal deadline has not passed</t>
         </is>
       </c>
-      <c r="H204" s="2" t="inlineStr">
+      <c r="H207" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_d@example.com
   2. Open "My Registrations"
   3. Withdraw from the event only</t>
         </is>
       </c>
-      <c r="I204" s="2" t="inlineStr">
+      <c r="I207" s="2" t="inlineStr">
         <is>
           <t>Withdrawing from: the event only</t>
         </is>
       </c>
-      <c r="J204" s="2" t="inlineStr">
+      <c r="J207" s="2" t="inlineStr">
         <is>
           <t>The the event registration is cancelled and its place becomes available again; attendee_d@example.com remains registered for the event</t>
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="2" t="n">
+    <row r="208">
+      <c r="A208" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B205" s="2" t="inlineStr">
+      <c r="B208" s="2" t="inlineStr">
         <is>
           <t>E09-S05</t>
         </is>
       </c>
-      <c r="C205" s="2" t="inlineStr">
+      <c r="C208" s="2" t="inlineStr">
         <is>
           <t>E09-S05 - Scenario 2 (Withdrawal after deadline refused)</t>
         </is>
       </c>
-      <c r="D205" s="2" t="inlineStr">
+      <c r="D208" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E205" s="2" t="inlineStr">
+      <c r="E208" s="2" t="inlineStr">
         <is>
           <t>TC_E09S05_03</t>
         </is>
       </c>
-      <c r="F205" s="2" t="inlineStr">
+      <c r="F208" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to withdraw after the withdrawal deadline has passed should be refused, with a contact provided for assistance</t>
         </is>
       </c>
-      <c r="G205" s="2" t="inlineStr">
+      <c r="G208" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s withdrawal deadline (10/12/2026) has passed</t>
         </is>
       </c>
-      <c r="H205" s="2" t="inlineStr">
+      <c r="H208" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_c@example.com
   2. Attempt to withdraw from "Community Meetup"</t>
         </is>
       </c>
-      <c r="I205" s="2" t="inlineStr">
+      <c r="I208" s="2" t="inlineStr">
         <is>
           <t>Withdrawal deadline: 10/12/2026 (passed)</t>
         </is>
       </c>
-      <c r="J205" s="2" t="inlineStr">
+      <c r="J208" s="2" t="inlineStr">
         <is>
           <t>Withdrawal is refused with the message "Withdrawal has closed" and a contact is provided for assistance</t>
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="2" t="n">
+    <row r="209">
+      <c r="A209" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B206" s="2" t="inlineStr">
+      <c r="B209" s="2" t="inlineStr">
         <is>
           <t>E09-S05</t>
         </is>
       </c>
-      <c r="C206" s="2" t="inlineStr">
+      <c r="C209" s="2" t="inlineStr">
         <is>
           <t>E09-S05 · Scenario 2 (Withdrawal after deadline refused)</t>
         </is>
       </c>
-      <c r="D206" s="2" t="inlineStr">
+      <c r="D209" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (exactly at)</t>
         </is>
       </c>
-      <c r="E206" s="2" t="inlineStr">
+      <c r="E209" s="2" t="inlineStr">
         <is>
           <t>TC_E09S05_04</t>
         </is>
       </c>
-      <c r="F206" s="2" t="inlineStr">
+      <c r="F209" s="2" t="inlineStr">
         <is>
           <t>Verify that withdrawal succeeds at the exact withdrawal deadline</t>
         </is>
       </c>
-      <c r="G206" s="2" t="inlineStr">
+      <c r="G209" s="2" t="inlineStr">
         <is>
           <t>Attendee attendee_a@example.com is registered for event EVT-2001. The withdrawal deadline for event EVT-2001 is 2026-10-25 23:59:59 +08:00</t>
         </is>
       </c>
-      <c r="H206" s="2" t="inlineStr">
+      <c r="H209" s="2" t="inlineStr">
         <is>
           <t>1. Set the system clock to exactly 2026-10-25 23:59:59 +08:00
  2. Sign in as attendee_a@example.com
  3. Open the registration for EVT-2001 and select Withdraw</t>
         </is>
       </c>
-      <c r="I206" s="2" t="inlineStr">
+      <c r="I209" s="2" t="inlineStr">
         <is>
           <t>Withdrawal deadline: 2026-10-25 23:59:59 +08:00 · Attempt at: 2026-10-25 23:59:59 +08:00</t>
         </is>
       </c>
-      <c r="J206" s="2" t="inlineStr">
+      <c r="J209" s="2" t="inlineStr">
         <is>
           <t>The withdrawal succeeds, the registration status becomes Withdrawn and the place is released. Every waitlisted Attendee for EVT-2001 is notified that a place is available
 ## E09-S06</t>
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="2" t="n">
+    <row r="210">
+      <c r="A210" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B207" s="2" t="inlineStr">
+      <c r="B210" s="2" t="inlineStr">
         <is>
           <t>E09-S06</t>
         </is>
       </c>
-      <c r="C207" s="2" t="inlineStr">
+      <c r="C210" s="2" t="inlineStr">
         <is>
           <t>E09-S06 - Scenario 1 (Attendance marked after completion)</t>
         </is>
       </c>
-      <c r="D207" s="2" t="inlineStr">
+      <c r="D210" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E207" s="2" t="inlineStr">
+      <c r="E210" s="2" t="inlineStr">
         <is>
           <t>TC_E09S06_01</t>
         </is>
       </c>
-      <c r="F207" s="2" t="inlineStr">
+      <c r="F210" s="2" t="inlineStr">
         <is>
           <t>Verify that marking a registered Attendee as attended for a event after the event is Completed should update their record without changing the registration figure</t>
         </is>
       </c>
-      <c r="G207" s="2" t="inlineStr">
+      <c r="G210" s="2" t="inlineStr">
         <is>
           <t>Event "Charity Run" has status "Completed" (per TC_E08S05_01); attendee_a@example.com is registered for its event</t>
         </is>
       </c>
-      <c r="H207" s="2" t="inlineStr">
+      <c r="H210" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the completed event "Charity Run"
   3. Mark attendee_a@example.com as "Attended"</t>
         </is>
       </c>
-      <c r="I207" s="2" t="inlineStr">
+      <c r="I210" s="2" t="inlineStr">
         <is>
           <t>Attendee: attendee_a@example.com</t>
         </is>
       </c>
-      <c r="J207" s="2" t="inlineStr">
+      <c r="J210" s="2" t="inlineStr">
         <is>
           <t>attendee_a@example.com's record shows "Attended"; the total registration figure for the event remains unchanged</t>
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="2" t="n">
+    <row r="211">
+      <c r="A211" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B208" s="2" t="inlineStr">
+      <c r="B211" s="2" t="inlineStr">
         <is>
           <t>E09-S06</t>
         </is>
       </c>
-      <c r="C208" s="2" t="inlineStr">
+      <c r="C211" s="2" t="inlineStr">
         <is>
           <t>E09-S06 - Scenario 2 (Registered but not attended)</t>
         </is>
       </c>
-      <c r="D208" s="2" t="inlineStr">
+      <c r="D211" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E208" s="2" t="inlineStr">
+      <c r="E211" s="2" t="inlineStr">
         <is>
           <t>TC_E09S06_02</t>
         </is>
       </c>
-      <c r="F208" s="2" t="inlineStr">
+      <c r="F211" s="2" t="inlineStr">
         <is>
           <t>Verify that a registered Attendee who did not attend should be shown as registered but not attended once the event is Completed</t>
         </is>
       </c>
-      <c r="G208" s="2" t="inlineStr">
+      <c r="G211" s="2" t="inlineStr">
         <is>
           <t>Event "Charity Run" has status "Completed"; attendee_b@example.com was registered but has not been marked attended</t>
         </is>
       </c>
-      <c r="H208" s="2" t="inlineStr">
+      <c r="H211" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the completed event "Charity Run"
   3. Check attendee_b@example.com's status</t>
         </is>
       </c>
-      <c r="I208" s="2" t="inlineStr">
+      <c r="I211" s="2" t="inlineStr">
         <is>
           <t>Attendee: attendee_b@example.com (registered, not marked attended)</t>
         </is>
       </c>
-      <c r="J208" s="2" t="inlineStr">
+      <c r="J211" s="2" t="inlineStr">
         <is>
           <t>attendee_b@example.com is shown as "Registered but not attended"</t>
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="2" t="n">
+    <row r="212">
+      <c r="A212" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B209" s="2" t="inlineStr">
+      <c r="B212" s="2" t="inlineStr">
         <is>
           <t>E09-S06</t>
         </is>
       </c>
-      <c r="C209" s="2" t="inlineStr">
+      <c r="C212" s="2" t="inlineStr">
         <is>
           <t>E09-S06 - Scenario 3 (Recording before completion blocked)</t>
         </is>
       </c>
-      <c r="D209" s="2" t="inlineStr">
+      <c r="D212" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E209" s="2" t="inlineStr">
+      <c r="E212" s="2" t="inlineStr">
         <is>
           <t>TC_E09S06_03</t>
         </is>
       </c>
-      <c r="F209" s="2" t="inlineStr">
+      <c r="F212" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to record attendance before the event is Completed should be blocked</t>
         </is>
       </c>
-      <c r="G209" s="2" t="inlineStr">
+      <c r="G212" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Conference 2026" has status "Confirmed" (not yet Completed)</t>
         </is>
       </c>
-      <c r="H209" s="2" t="inlineStr">
+      <c r="H212" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Tech Conference 2026"
   3. Attempt to mark an Attendee as attended</t>
         </is>
       </c>
-      <c r="I209" s="2" t="inlineStr">
+      <c r="I212" s="2" t="inlineStr">
         <is>
           <t>Event status: Confirmed (not Completed)</t>
         </is>
       </c>
-      <c r="J209" s="2" t="inlineStr">
+      <c r="J212" s="2" t="inlineStr">
         <is>
           <t>The action is blocked; attendance cannot be recorded before the event is Completed</t>
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="2" t="n">
+    <row r="213">
+      <c r="A213" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B210" s="2" t="inlineStr">
+      <c r="B213" s="2" t="inlineStr">
         <is>
           <t>E09-S06</t>
         </is>
       </c>
-      <c r="C210" s="2" t="inlineStr">
+      <c r="C213" s="2" t="inlineStr">
         <is>
           <t>E09-S06 (checklist: registration/attendance counts viewable side by side)</t>
         </is>
       </c>
-      <c r="D210" s="2" t="inlineStr">
+      <c r="D213" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E210" s="2" t="inlineStr">
+      <c r="E213" s="2" t="inlineStr">
         <is>
           <t>TC_E09S06_04</t>
         </is>
       </c>
-      <c r="F210" s="2" t="inlineStr">
+      <c r="F213" s="2" t="inlineStr">
         <is>
           <t>Verify that registration and attendance counts should be viewable side by side for each event</t>
         </is>
       </c>
-      <c r="G210" s="2" t="inlineStr">
+      <c r="G213" s="2" t="inlineStr">
         <is>
           <t>Event "Charity Run" has status "Completed"; its event had 5 registrations and 4 marked attended</t>
         </is>
       </c>
-      <c r="H210" s="2" t="inlineStr">
+      <c r="H213" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the completed event "Charity Run"
   3. View the event's registration and attendance summary</t>
         </is>
       </c>
-      <c r="I210" s="2" t="inlineStr">
+      <c r="I213" s="2" t="inlineStr">
         <is>
           <t>Registered: 5 | Attended: 4</t>
         </is>
       </c>
-      <c r="J210" s="2" t="inlineStr">
+      <c r="J213" s="2" t="inlineStr">
         <is>
           <t>The summary shows "Registered: 5" and "Attended: 4" together, side by side
 ## E09-S07</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B211" s="2" t="inlineStr">
-        <is>
-          <t>E09-S07</t>
-        </is>
-      </c>
-      <c r="C211" s="2" t="inlineStr">
-        <is>
-          <t>E09-S07 - Scenario 1 (Registrations grouped by event)</t>
-        </is>
-      </c>
-      <c r="D211" s="2" t="inlineStr">
-        <is>
-          <t>2 - Happy Path</t>
-        </is>
-      </c>
-      <c r="E211" s="2" t="inlineStr">
-        <is>
-          <t>TC_E09S07_01</t>
-        </is>
-      </c>
-      <c r="F211" s="2" t="inlineStr">
-        <is>
-          <t>Verify that opening the registration list for an event with registered Attendees should show each Attendee's name, email address and contact number</t>
-        </is>
-      </c>
-      <c r="G211" s="2" t="inlineStr">
-        <is>
-          <t>Event "Tech Conference 2026" has attendee_a@example.com and attendee_b@example.com registered, each with a name, email address and contact number on file</t>
-        </is>
-      </c>
-      <c r="H211" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in as organiser_a@clienta.com
-  2. Open the registration list for "Tech Conference 2026"</t>
-        </is>
-      </c>
-      <c r="I211" s="2" t="inlineStr">
-        <is>
-          <t>attendee_a@example.com: +65 9123 4567 | attendee_b@example.com: +65 9234 5678</t>
-        </is>
-      </c>
-      <c r="J211" s="2" t="inlineStr">
-        <is>
-          <t>The list shows each Attendee's name, email address and contact number: attendee_a@example.com and attendee_b@example.com both appear with their full contact details</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B212" s="2" t="inlineStr">
-        <is>
-          <t>E09-S07</t>
-        </is>
-      </c>
-      <c r="C212" s="2" t="inlineStr">
-        <is>
-          <t>E09-S07 - Scenario 2 (Counts and remaining capacity)</t>
-        </is>
-      </c>
-      <c r="D212" s="2" t="inlineStr">
-        <is>
-          <t>2 - Happy Path</t>
-        </is>
-      </c>
-      <c r="E212" s="2" t="inlineStr">
-        <is>
-          <t>TC_E09S07_02</t>
-        </is>
-      </c>
-      <c r="F212" s="2" t="inlineStr">
-        <is>
-          <t>Verify that the registration list should show the registered count and remaining capacity per event</t>
-        </is>
-      </c>
-      <c r="G212" s="2" t="inlineStr">
-        <is>
-          <t>"Tech Conference 2026" the event has 100 registered out of a capacity of 150</t>
-        </is>
-      </c>
-      <c r="H212" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in as organiser_a@clienta.com
-  2. Open the registration list for "Tech Conference 2026"</t>
-        </is>
-      </c>
-      <c r="I212" s="2" t="inlineStr">
-        <is>
-          <t>the event: 100 registered, capacity 150</t>
-        </is>
-      </c>
-      <c r="J212" s="2" t="inlineStr">
-        <is>
-          <t>the event shows "100 registered" and "50 remaining"</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B213" s="2" t="inlineStr">
-        <is>
-          <t>E09-S07</t>
-        </is>
-      </c>
-      <c r="C213" s="2" t="inlineStr">
-        <is>
-          <t>E09-S07 - Scenario 3 (Unmanaged event refused)</t>
-        </is>
-      </c>
-      <c r="D213" s="2" t="inlineStr">
-        <is>
-          <t>4 - Negative</t>
-        </is>
-      </c>
-      <c r="E213" s="2" t="inlineStr">
-        <is>
-          <t>TC_E09S07_03</t>
-        </is>
-      </c>
-      <c r="F213" s="2" t="inlineStr">
-        <is>
-          <t>Verify that attempting to open the registration list for an event that does not belong to the Organiser's client organisation should be refused</t>
-        </is>
-      </c>
-      <c r="G213" s="2" t="inlineStr">
-        <is>
-          <t>organiser_b@clienta.com is linked to Client B; event "Annual Tech Summit" belongs to Client A</t>
-        </is>
-      </c>
-      <c r="H213" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in as organiser_b@clienta.com
-  2. Attempt to open the registration list for "Annual Tech Summit"</t>
-        </is>
-      </c>
-      <c r="I213" s="2" t="inlineStr">
-        <is>
-          <t>Acting user: organiser_b@clienta.com | Event: Annual Tech Summit (Client A)</t>
-        </is>
-      </c>
-      <c r="J213" s="2" t="inlineStr">
-        <is>
-          <t>Access is refused, since "Annual Tech Summit" does not belong to organiser_b@clienta.com's client organisation</t>
         </is>
       </c>
     </row>
@@ -11627,7 +11636,7 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>E09-S07 - Scenario 4 (Waitlist shown separately)</t>
+          <t>E09-S07 - Scenario 1 (Registrations grouped by event)</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
@@ -11637,33 +11646,33 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>TC_E09S07_04</t>
+          <t>TC_E09S07_01</t>
         </is>
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
-          <t>Verify that waitlisted Attendees should be shown separately from registered Attendees on the registration list</t>
+          <t>Verify that opening the registration list for an event with registered Attendees should show each Attendee's name, email address and contact number</t>
         </is>
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>"Community Meetup"'s event has 5 registered Attendees and 2 on the waiting list</t>
+          <t>Event "Tech Conference 2026" has attendee_a@example.com and attendee_b@example.com registered, each with a name, email address and contact number on file</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
-  2. Open the registration list for "Community Meetup"</t>
+  2. Open the registration list for "Tech Conference 2026"</t>
         </is>
       </c>
       <c r="I214" s="2" t="inlineStr">
         <is>
-          <t>Registered: 5 | Waitlisted: 2</t>
+          <t>attendee_a@example.com: +65 9123 4567 | attendee_b@example.com: +65 9234 5678</t>
         </is>
       </c>
       <c r="J214" s="2" t="inlineStr">
         <is>
-          <t>The 5 registered Attendees and the 2 waitlisted Attendees are shown in clearly separate sections/lists</t>
+          <t>The list shows each Attendee's name, email address and contact number: attendee_a@example.com and attendee_b@example.com both appear with their full contact details</t>
         </is>
       </c>
     </row>
@@ -11673,35 +11682,188 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
+          <t>E09-S07</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>E09-S07 - Scenario 2 (Counts and remaining capacity)</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>2 - Happy Path</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>TC_E09S07_02</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>Verify that the registration list should show the registered count and remaining capacity per event</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>"Tech Conference 2026" the event has 100 registered out of a capacity of 150</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in as organiser_a@clienta.com
+  2. Open the registration list for "Tech Conference 2026"</t>
+        </is>
+      </c>
+      <c r="I215" s="2" t="inlineStr">
+        <is>
+          <t>the event: 100 registered, capacity 150</t>
+        </is>
+      </c>
+      <c r="J215" s="2" t="inlineStr">
+        <is>
+          <t>the event shows "100 registered" and "50 remaining"</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>E09-S07</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>E09-S07 - Scenario 3 (Unmanaged event refused)</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>4 - Negative</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>TC_E09S07_03</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>Verify that attempting to open the registration list for an event that does not belong to the Organiser's client organisation should be refused</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>organiser_b@clienta.com is linked to Client B; event "Annual Tech Summit" belongs to Client A</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in as organiser_b@clienta.com
+  2. Attempt to open the registration list for "Annual Tech Summit"</t>
+        </is>
+      </c>
+      <c r="I216" s="2" t="inlineStr">
+        <is>
+          <t>Acting user: organiser_b@clienta.com | Event: Annual Tech Summit (Client A)</t>
+        </is>
+      </c>
+      <c r="J216" s="2" t="inlineStr">
+        <is>
+          <t>Access is refused, since "Annual Tech Summit" does not belong to organiser_b@clienta.com's client organisation</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>E09-S07</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>E09-S07 - Scenario 4 (Waitlist shown separately)</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>2 - Happy Path</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>TC_E09S07_04</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>Verify that waitlisted Attendees should be shown separately from registered Attendees on the registration list</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>"Community Meetup"'s event has 5 registered Attendees and 2 on the waiting list</t>
+        </is>
+      </c>
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in as organiser_a@clienta.com
+  2. Open the registration list for "Community Meetup"</t>
+        </is>
+      </c>
+      <c r="I217" s="2" t="inlineStr">
+        <is>
+          <t>Registered: 5 | Waitlisted: 2</t>
+        </is>
+      </c>
+      <c r="J217" s="2" t="inlineStr">
+        <is>
+          <t>The 5 registered Attendees and the 2 waitlisted Attendees are shown in clearly separate sections/lists</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
           <t>E10-S01</t>
         </is>
       </c>
-      <c r="C215" s="2" t="inlineStr">
+      <c r="C218" s="2" t="inlineStr">
         <is>
           <t>E10-S01 - Scenario 1 (Change request recorded)</t>
         </is>
       </c>
-      <c r="D215" s="2" t="inlineStr">
+      <c r="D218" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E215" s="2" t="inlineStr">
+      <c r="E218" s="2" t="inlineStr">
         <is>
           <t>TC_E10S01_01</t>
         </is>
       </c>
-      <c r="F215" s="2" t="inlineStr">
+      <c r="F218" s="2" t="inlineStr">
         <is>
           <t>Verify that submitting a change request on an approved or confirmed event should notify the assigned Coordinator and record the request against the event</t>
         </is>
       </c>
-      <c r="G215" s="2" t="inlineStr">
+      <c r="G218" s="2" t="inlineStr">
         <is>
           <t>Event "Community Meetup" has status "Confirmed"</t>
         </is>
       </c>
-      <c r="H215" s="2" t="inlineStr">
+      <c r="H218" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open event "Community Meetup"
@@ -11710,155 +11872,155 @@
   5. Submit</t>
         </is>
       </c>
-      <c r="I215" s="2" t="inlineStr">
+      <c r="I218" s="2" t="inlineStr">
         <is>
           <t>Change description: "Increase expected attendance to 10"</t>
         </is>
       </c>
-      <c r="J215" s="2" t="inlineStr">
+      <c r="J218" s="2" t="inlineStr">
         <is>
           <t>coordinator_1@connectsphere.com is notified, and the change request is recorded against "Community Meetup"</t>
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="2" t="n">
+    <row r="219">
+      <c r="A219" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B216" s="2" t="inlineStr">
+      <c r="B219" s="2" t="inlineStr">
         <is>
           <t>E10-S01</t>
         </is>
       </c>
-      <c r="C216" s="2" t="inlineStr">
+      <c r="C219" s="2" t="inlineStr">
         <is>
           <t>E10-S01 - Scenario 2 (Confirmed details shown alongside)</t>
         </is>
       </c>
-      <c r="D216" s="2" t="inlineStr">
+      <c r="D219" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E216" s="2" t="inlineStr">
+      <c r="E219" s="2" t="inlineStr">
         <is>
           <t>TC_E10S01_02</t>
         </is>
       </c>
-      <c r="F216" s="2" t="inlineStr">
+      <c r="F219" s="2" t="inlineStr">
         <is>
           <t>Verify that viewing an event with a pending change request should still show the currently confirmed details alongside the pending request</t>
         </is>
       </c>
-      <c r="G216" s="2" t="inlineStr">
+      <c r="G219" s="2" t="inlineStr">
         <is>
           <t>Event "Community Meetup" has a pending change request; its confirmed details (venue, date, time) remain unchanged</t>
         </is>
       </c>
-      <c r="H216" s="2" t="inlineStr">
+      <c r="H219" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open event "Community Meetup"</t>
         </is>
       </c>
-      <c r="I216" s="2" t="inlineStr">
+      <c r="I219" s="2" t="inlineStr">
         <is>
           <t>Pending request: Increase expected attendance to 10</t>
         </is>
       </c>
-      <c r="J216" s="2" t="inlineStr">
+      <c r="J219" s="2" t="inlineStr">
         <is>
           <t>The page shows both the currently confirmed details and the pending change request together</t>
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="2" t="n">
+    <row r="220">
+      <c r="A220" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B217" s="2" t="inlineStr">
+      <c r="B220" s="2" t="inlineStr">
         <is>
           <t>E10-S01</t>
         </is>
       </c>
-      <c r="C217" s="2" t="inlineStr">
+      <c r="C220" s="2" t="inlineStr">
         <is>
           <t>E10-S01 - Scenario 3 (Refused edit offers the form)</t>
         </is>
       </c>
-      <c r="D217" s="2" t="inlineStr">
+      <c r="D220" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E217" s="2" t="inlineStr">
+      <c r="E220" s="2" t="inlineStr">
         <is>
           <t>TC_E10S01_03</t>
         </is>
       </c>
-      <c r="F217" s="2" t="inlineStr">
+      <c r="F220" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to directly edit a restricted field after approval should be refused and offered the change request form pre-filled with that field</t>
         </is>
       </c>
-      <c r="G217" s="2" t="inlineStr">
+      <c r="G220" s="2" t="inlineStr">
         <is>
           <t>Event "Community Meetup" has status "Confirmed"</t>
         </is>
       </c>
-      <c r="H217" s="2" t="inlineStr">
+      <c r="H220" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open event "Community Meetup"
   3. Attempt to directly edit the Expected Attendance field</t>
         </is>
       </c>
-      <c r="I217" s="2" t="inlineStr">
+      <c r="I220" s="2" t="inlineStr">
         <is>
           <t>Field attempted: Expected Attendance</t>
         </is>
       </c>
-      <c r="J217" s="2" t="inlineStr">
+      <c r="J220" s="2" t="inlineStr">
         <is>
           <t>Direct editing is refused; organiser_a@clienta.com is offered the change request form, pre-filled with the Expected Attendance field</t>
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="2" t="n">
+    <row r="221">
+      <c r="A221" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B218" s="2" t="inlineStr">
+      <c r="B221" s="2" t="inlineStr">
         <is>
           <t>E10-S01</t>
         </is>
       </c>
-      <c r="C218" s="2" t="inlineStr">
+      <c r="C221" s="2" t="inlineStr">
         <is>
           <t>E10-S01 - Scenario 4 (Approved change applied)</t>
         </is>
       </c>
-      <c r="D218" s="2" t="inlineStr">
+      <c r="D221" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E218" s="2" t="inlineStr">
+      <c r="E221" s="2" t="inlineStr">
         <is>
           <t>TC_E10S01_04</t>
         </is>
       </c>
-      <c r="F218" s="2" t="inlineStr">
+      <c r="F221" s="2" t="inlineStr">
         <is>
           <t>Verify that when the Coordinator approves a change request, the event should be updated and the Organiser notified</t>
         </is>
       </c>
-      <c r="G218" s="2" t="inlineStr">
+      <c r="G221" s="2" t="inlineStr">
         <is>
           <t>A change request on "Community Meetup" (increase expected attendance to 10) is pending Coordinator approval</t>
         </is>
       </c>
-      <c r="H218" s="2" t="inlineStr">
+      <c r="H221" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the pending change request
@@ -11866,52 +12028,52 @@
   4. Log in as organiser_a@clienta.com and check the event and notifications</t>
         </is>
       </c>
-      <c r="I218" s="2" t="inlineStr">
+      <c r="I221" s="2" t="inlineStr">
         <is>
           <t>Change: Expected Attendance -&gt; 10</t>
         </is>
       </c>
-      <c r="J218" s="2" t="inlineStr">
+      <c r="J221" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s Expected Attendance is updated to 10, and organiser_a@clienta.com is notified that the change was applied</t>
         </is>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" s="2" t="n">
+    <row r="222">
+      <c r="A222" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B219" s="2" t="inlineStr">
+      <c r="B222" s="2" t="inlineStr">
         <is>
           <t>E10-S01</t>
         </is>
       </c>
-      <c r="C219" s="2" t="inlineStr">
+      <c r="C222" s="2" t="inlineStr">
         <is>
           <t>E10-S01 (checklist: notified when Coordinator approves or declines)</t>
         </is>
       </c>
-      <c r="D219" s="2" t="inlineStr">
+      <c r="D222" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E219" s="2" t="inlineStr">
+      <c r="E222" s="2" t="inlineStr">
         <is>
           <t>TC_E10S01_05</t>
         </is>
       </c>
-      <c r="F219" s="2" t="inlineStr">
+      <c r="F222" s="2" t="inlineStr">
         <is>
           <t>Verify that when the Coordinator declines a change request, the Organiser should be notified</t>
         </is>
       </c>
-      <c r="G219" s="2" t="inlineStr">
+      <c r="G222" s="2" t="inlineStr">
         <is>
           <t>A change request on "Community Meetup" is pending Coordinator approval</t>
         </is>
       </c>
-      <c r="H219" s="2" t="inlineStr">
+      <c r="H222" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the pending change request
@@ -11920,105 +12082,105 @@
   5. Log in as organiser_a@clienta.com and check notifications</t>
         </is>
       </c>
-      <c r="I219" s="2" t="inlineStr">
+      <c r="I222" s="2" t="inlineStr">
         <is>
           <t>Decision: Declined</t>
         </is>
       </c>
-      <c r="J219" s="2" t="inlineStr">
+      <c r="J222" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com is notified that the change request was declined, and the event remains unchanged
 ## E10-S02</t>
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="2" t="n">
+    <row r="223">
+      <c r="A223" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B220" s="2" t="inlineStr">
+      <c r="B223" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="C220" s="2" t="inlineStr">
+      <c r="C223" s="2" t="inlineStr">
         <is>
           <t>E10-S02 - Scenario 1 (Attendance beyond capacity flagged)</t>
         </is>
       </c>
-      <c r="D220" s="2" t="inlineStr">
+      <c r="D223" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E220" s="2" t="inlineStr">
+      <c r="E223" s="2" t="inlineStr">
         <is>
           <t>TC_E10S02_01</t>
         </is>
       </c>
-      <c r="F220" s="2" t="inlineStr">
+      <c r="F223" s="2" t="inlineStr">
         <is>
           <t>Verify that increasing a event's expected attendance beyond its confirmed venue's capacity should flag the venue booking for review and notify Venue Staff</t>
         </is>
       </c>
-      <c r="G220" s="2" t="inlineStr">
+      <c r="G223" s="2" t="inlineStr">
         <is>
           <t>A event of "Tech Conference 2026" has a confirmed venue "Riverside Hall" with capacity 200</t>
         </is>
       </c>
-      <c r="H220" s="2" t="inlineStr">
+      <c r="H223" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Increase the event's Expected Attendance to 250
   3. Save</t>
         </is>
       </c>
-      <c r="I220" s="2" t="inlineStr">
+      <c r="I223" s="2" t="inlineStr">
         <is>
           <t>Expected Attendance: 200 -&gt; 250 (venue capacity: 200)</t>
         </is>
       </c>
-      <c r="J220" s="2" t="inlineStr">
+      <c r="J223" s="2" t="inlineStr">
         <is>
           <t>The venue booking for "Riverside Hall" is flagged for review, and venue_staff_1@connectsphere.com is notified</t>
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="2" t="n">
+    <row r="224">
+      <c r="A224" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B221" s="2" t="inlineStr">
+      <c r="B224" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="C221" s="2" t="inlineStr">
+      <c r="C224" s="2" t="inlineStr">
         <is>
           <t>E10-S02 - Scenario 2 (Description-only edit flags nothing)</t>
         </is>
       </c>
-      <c r="D221" s="2" t="inlineStr">
+      <c r="D224" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E221" s="2" t="inlineStr">
+      <c r="E224" s="2" t="inlineStr">
         <is>
           <t>TC_E10S02_02</t>
         </is>
       </c>
-      <c r="F221" s="2" t="inlineStr">
+      <c r="F224" s="2" t="inlineStr">
         <is>
           <t>Verify that editing only the event description on an event with confirmed venue and equipment should flag nothing</t>
         </is>
       </c>
-      <c r="G221" s="2" t="inlineStr">
+      <c r="G224" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Conference 2026" has a confirmed venue and equipment</t>
         </is>
       </c>
-      <c r="H221" s="2" t="inlineStr">
+      <c r="H224" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Edit only the Description field
@@ -12026,208 +12188,208 @@
   4. Check for any flagged arrangements</t>
         </is>
       </c>
-      <c r="I221" s="2" t="inlineStr">
+      <c r="I224" s="2" t="inlineStr">
         <is>
           <t>Field changed: Description only</t>
         </is>
       </c>
-      <c r="J221" s="2" t="inlineStr">
+      <c r="J224" s="2" t="inlineStr">
         <is>
           <t>No arrangements are flagged as a result of this edit</t>
         </is>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" s="2" t="n">
+    <row r="225">
+      <c r="A225" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B222" s="2" t="inlineStr">
+      <c r="B225" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="C222" s="2" t="inlineStr">
+      <c r="C225" s="2" t="inlineStr">
         <is>
           <t>E10-S02 - Scenario 3 (Affected arrangements shown first)</t>
         </is>
       </c>
-      <c r="D222" s="2" t="inlineStr">
+      <c r="D225" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E222" s="2" t="inlineStr">
+      <c r="E225" s="2" t="inlineStr">
         <is>
           <t>TC_E10S02_03</t>
         </is>
       </c>
-      <c r="F222" s="2" t="inlineStr">
+      <c r="F225" s="2" t="inlineStr">
         <is>
           <t>Verify that saving a change that affects confirmed arrangements should show which arrangements are affected before the change takes effect</t>
         </is>
       </c>
-      <c r="G222" s="2" t="inlineStr">
+      <c r="G225" s="2" t="inlineStr">
         <is>
           <t>A pending edit to "Tech Conference 2026" would affect its confirmed venue booking</t>
         </is>
       </c>
-      <c r="H222" s="2" t="inlineStr">
+      <c r="H225" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Make the edit that affects the venue booking
   3. Click "Save"</t>
         </is>
       </c>
-      <c r="I222" s="2" t="inlineStr">
+      <c r="I225" s="2" t="inlineStr">
         <is>
           <t>Edit: affects the confirmed venue booking</t>
         </is>
       </c>
-      <c r="J222" s="2" t="inlineStr">
+      <c r="J225" s="2" t="inlineStr">
         <is>
           <t>Before the change is applied, a confirmation screen lists the affected arrangement (venue booking) for review</t>
         </is>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" s="2" t="n">
+    <row r="226">
+      <c r="A226" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B223" s="2" t="inlineStr">
+      <c r="B226" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="C223" s="2" t="inlineStr">
+      <c r="C226" s="2" t="inlineStr">
         <is>
           <t>E10-S02 - Scenario 4 (Over-subscription warns only)</t>
         </is>
       </c>
-      <c r="D223" s="2" t="inlineStr">
+      <c r="D226" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E223" s="2" t="inlineStr">
+      <c r="E226" s="2" t="inlineStr">
         <is>
           <t>TC_E10S02_04</t>
         </is>
       </c>
-      <c r="F223" s="2" t="inlineStr">
+      <c r="F226" s="2" t="inlineStr">
         <is>
           <t>Verify that a venue change that reduces a event's capacity below its registration count should warn the Coordinator and show the over-subscription without automatically removing or waitlisting anyone</t>
         </is>
       </c>
-      <c r="G223" s="2" t="inlineStr">
+      <c r="G226" s="2" t="inlineStr">
         <is>
           <t>A event of "Tech Conference 2026" has 100 registered; a venue change is about to reduce its capacity to 80</t>
         </is>
       </c>
-      <c r="H223" s="2" t="inlineStr">
+      <c r="H226" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Change the event's venue to one with capacity 80
   3. Save</t>
         </is>
       </c>
-      <c r="I223" s="2" t="inlineStr">
+      <c r="I226" s="2" t="inlineStr">
         <is>
           <t>New capacity: 80; Registered: 100</t>
         </is>
       </c>
-      <c r="J223" s="2" t="inlineStr">
+      <c r="J226" s="2" t="inlineStr">
         <is>
           <t>coordinator_1@connectsphere.com is warned and shown the over-subscription (100 vs 80); no Attendee is automatically removed or waitlisted</t>
         </is>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" s="2" t="n">
+    <row r="227">
+      <c r="A227" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B224" s="2" t="inlineStr">
+      <c r="B227" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="C224" s="2" t="inlineStr">
+      <c r="C227" s="2" t="inlineStr">
         <is>
           <t>E10-S02 - Scenario 5 (Date change flags venue and equipment)</t>
         </is>
       </c>
-      <c r="D224" s="2" t="inlineStr">
+      <c r="D227" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E224" s="2" t="inlineStr">
+      <c r="E227" s="2" t="inlineStr">
         <is>
           <t>TC_E10S02_05</t>
         </is>
       </c>
-      <c r="F224" s="2" t="inlineStr">
+      <c r="F227" s="2" t="inlineStr">
         <is>
           <t>Verify that changing a event's date or time should flag its venue booking and equipment reservations as requiring reconfirmation</t>
         </is>
       </c>
-      <c r="G224" s="2" t="inlineStr">
+      <c r="G227" s="2" t="inlineStr">
         <is>
           <t>A event of "Tech Conference 2026" has a confirmed venue and reserved equipment</t>
         </is>
       </c>
-      <c r="H224" s="2" t="inlineStr">
+      <c r="H227" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Change the event's date from 15/11/2026 to 20/11/2026
   3. Save</t>
         </is>
       </c>
-      <c r="I224" s="2" t="inlineStr">
+      <c r="I227" s="2" t="inlineStr">
         <is>
           <t>Date: 15/11/2026 -&gt; 20/11/2026</t>
         </is>
       </c>
-      <c r="J224" s="2" t="inlineStr">
+      <c r="J227" s="2" t="inlineStr">
         <is>
           <t>Both the venue booking and the equipment reservations for this event are flagged as requiring reconfirmation</t>
         </is>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" s="2" t="n">
+    <row r="228">
+      <c r="A228" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B225" s="2" t="inlineStr">
+      <c r="B228" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="C225" s="2" t="inlineStr">
+      <c r="C228" s="2" t="inlineStr">
         <is>
           <t>E10-S02 (checklist: Venue Staff and Technical Support Staff both notified)</t>
         </is>
       </c>
-      <c r="D225" s="2" t="inlineStr">
+      <c r="D228" s="2" t="inlineStr">
         <is>
           <t>3 - Cross-cutting (notification consistency)</t>
         </is>
       </c>
-      <c r="E225" s="2" t="inlineStr">
+      <c r="E228" s="2" t="inlineStr">
         <is>
           <t>TC_E10S02_06</t>
         </is>
       </c>
-      <c r="F225" s="2" t="inlineStr">
+      <c r="F228" s="2" t="inlineStr">
         <is>
           <t>Verify that when a date or time change flags arrangements for reconfirmation, the assigned Technical Support Staff should also be notified, not just Venue Staff</t>
         </is>
       </c>
-      <c r="G225" s="2" t="inlineStr">
+      <c r="G228" s="2" t="inlineStr">
         <is>
           <t>A event of "Tech Conference 2026" has a confirmed venue, reserved equipment, and tech_support_1@connectsphere.com assigned for on-site support</t>
         </is>
       </c>
-      <c r="H225" s="2" t="inlineStr">
+      <c r="H228" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Change the event's date
@@ -12235,53 +12397,53 @@
   4. Check notifications for both venue_staff_1@connectsphere.com and tech_support_1@connectsphere.com</t>
         </is>
       </c>
-      <c r="I225" s="2" t="inlineStr">
+      <c r="I228" s="2" t="inlineStr">
         <is>
           <t>Changed field: Date</t>
         </is>
       </c>
-      <c r="J225" s="2" t="inlineStr">
+      <c r="J228" s="2" t="inlineStr">
         <is>
           <t>Both venue_staff_1@connectsphere.com and tech_support_1@connectsphere.com receive a notification about the change requiring reconfirmation
 ## E10-S04</t>
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="2" t="n">
+    <row r="229">
+      <c r="A229" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B226" s="2" t="inlineStr">
+      <c r="B229" s="2" t="inlineStr">
         <is>
           <t>E10-S04</t>
         </is>
       </c>
-      <c r="C226" s="2" t="inlineStr">
+      <c r="C229" s="2" t="inlineStr">
         <is>
           <t>E10-S04 - Scenario 1 (Event cancelled, arrangements released)</t>
         </is>
       </c>
-      <c r="D226" s="2" t="inlineStr">
+      <c r="D229" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E226" s="2" t="inlineStr">
+      <c r="E229" s="2" t="inlineStr">
         <is>
           <t>TC_E10S04_01</t>
         </is>
       </c>
-      <c r="F226" s="2" t="inlineStr">
+      <c r="F229" s="2" t="inlineStr">
         <is>
           <t>Verify that cancelling an event and recording a reason should release its venue bookings and equipment reservations, update the venue calendars, and notify affected staff</t>
         </is>
       </c>
-      <c r="G226" s="2" t="inlineStr">
+      <c r="G229" s="2" t="inlineStr">
         <is>
           <t>Event "Product Launch Night" has status "Confirmed" with a confirmed venue "Small Room" and reserved equipment</t>
         </is>
       </c>
-      <c r="H226" s="2" t="inlineStr">
+      <c r="H229" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Product Launch Night"
@@ -12290,156 +12452,156 @@
   5. Confirm</t>
         </is>
       </c>
-      <c r="I226" s="2" t="inlineStr">
+      <c r="I229" s="2" t="inlineStr">
         <is>
           <t>Cancellation reason: "Insufficient sponsor funding"</t>
         </is>
       </c>
-      <c r="J226" s="2" t="inlineStr">
+      <c r="J229" s="2" t="inlineStr">
         <is>
           <t>The status becomes "Cancelled"; "Small Room"'s booking and the reserved equipment are released, the venue calendar is updated, and affected staff are notified</t>
         </is>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="2" t="n">
+    <row r="230">
+      <c r="A230" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B227" s="2" t="inlineStr">
+      <c r="B230" s="2" t="inlineStr">
         <is>
           <t>E10-S04</t>
         </is>
       </c>
-      <c r="C227" s="2" t="inlineStr">
+      <c r="C230" s="2" t="inlineStr">
         <is>
           <t>E10-S04 - Scenario 2 (Attendees and waitlist notified)</t>
         </is>
       </c>
-      <c r="D227" s="2" t="inlineStr">
+      <c r="D230" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E227" s="2" t="inlineStr">
+      <c r="E230" s="2" t="inlineStr">
         <is>
           <t>TC_E10S04_03</t>
         </is>
       </c>
-      <c r="F227" s="2" t="inlineStr">
+      <c r="F230" s="2" t="inlineStr">
         <is>
           <t>Verify that cancelling a event should notify all of its registered and waitlisted Attendees</t>
         </is>
       </c>
-      <c r="G227" s="2" t="inlineStr">
+      <c r="G230" s="2" t="inlineStr">
         <is>
           <t>The event of "Tech Conference 2026" being cancelled has attendee_a@example.com registered and attendee_l@example.com waitlisted</t>
         </is>
       </c>
-      <c r="H227" s="2" t="inlineStr">
+      <c r="H230" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Cancel the event
   3. Check notifications for attendee_a@example.com and attendee_l@example.com</t>
         </is>
       </c>
-      <c r="I227" s="2" t="inlineStr">
+      <c r="I230" s="2" t="inlineStr">
         <is>
           <t>Registered: attendee_a@example.com | Waitlisted: attendee_l@example.com</t>
         </is>
       </c>
-      <c r="J227" s="2" t="inlineStr">
+      <c r="J230" s="2" t="inlineStr">
         <is>
           <t>Both attendee_a@example.com and attendee_l@example.com receive a notification of the cancellation</t>
         </is>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" s="2" t="n">
+    <row r="231">
+      <c r="A231" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B228" s="2" t="inlineStr">
+      <c r="B231" s="2" t="inlineStr">
         <is>
           <t>E10-S04</t>
         </is>
       </c>
-      <c r="C228" s="2" t="inlineStr">
+      <c r="C231" s="2" t="inlineStr">
         <is>
           <t>E10-S04 - Scenario 3 (Cancelled event read-only)</t>
         </is>
       </c>
-      <c r="D228" s="2" t="inlineStr">
+      <c r="D231" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E228" s="2" t="inlineStr">
+      <c r="E231" s="2" t="inlineStr">
         <is>
           <t>TC_E10S04_04</t>
         </is>
       </c>
-      <c r="F228" s="2" t="inlineStr">
+      <c r="F231" s="2" t="inlineStr">
         <is>
           <t>Verify that a cancelled event should be read-only and show its cancellation reason and date to any viewer</t>
         </is>
       </c>
-      <c r="G228" s="2" t="inlineStr">
+      <c r="G231" s="2" t="inlineStr">
         <is>
           <t>Event "Product Launch Night" was cancelled on 12/09/2026 with reason "Insufficient sponsor funding" (per TC_E10S04_01)</t>
         </is>
       </c>
-      <c r="H228" s="2" t="inlineStr">
+      <c r="H231" s="2" t="inlineStr">
         <is>
           <t>1. Log in as any user with access (e.g. organiser_a@clienta.com)
   2. Open the cancelled event "Product Launch Night"
   3. Attempt to edit any field</t>
         </is>
       </c>
-      <c r="I228" s="2" t="inlineStr">
+      <c r="I231" s="2" t="inlineStr">
         <is>
           <t>Cancellation reason: "Insufficient sponsor funding" | Date: 12/09/2026</t>
         </is>
       </c>
-      <c r="J228" s="2" t="inlineStr">
+      <c r="J231" s="2" t="inlineStr">
         <is>
           <t>The event shows "Cancelled on 12 September 2026 - Insufficient sponsor funding"; all fields are read-only</t>
         </is>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" s="2" t="n">
+    <row r="232">
+      <c r="A232" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B229" s="2" t="inlineStr">
+      <c r="B232" s="2" t="inlineStr">
         <is>
           <t>E10-S04</t>
         </is>
       </c>
-      <c r="C229" s="2" t="inlineStr">
+      <c r="C232" s="2" t="inlineStr">
         <is>
           <t>E10-S04 - Scenario 4 (Organiser cancellation becomes a request)</t>
         </is>
       </c>
-      <c r="D229" s="2" t="inlineStr">
+      <c r="D232" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E229" s="2" t="inlineStr">
+      <c r="E232" s="2" t="inlineStr">
         <is>
           <t>TC_E10S04_05</t>
         </is>
       </c>
-      <c r="F229" s="2" t="inlineStr">
+      <c r="F232" s="2" t="inlineStr">
         <is>
           <t>Verify that an Event Organiser attempting to cancel directly should have the action recorded as a cancellation request for the Coordinator to action</t>
         </is>
       </c>
-      <c r="G229" s="2" t="inlineStr">
+      <c r="G232" s="2" t="inlineStr">
         <is>
           <t>Event "Community Meetup" has status "Confirmed", assigned to coordinator_1@connectsphere.com</t>
         </is>
       </c>
-      <c r="H229" s="2" t="inlineStr">
+      <c r="H232" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open event "Community Meetup"
@@ -12447,167 +12609,14 @@
   4. Enter a reason and submit</t>
         </is>
       </c>
-      <c r="I229" s="2" t="inlineStr">
+      <c r="I232" s="2" t="inlineStr">
         <is>
           <t>Reason: "No longer needed"</t>
         </is>
       </c>
-      <c r="J229" s="2" t="inlineStr">
+      <c r="J232" s="2" t="inlineStr">
         <is>
           <t>The event is NOT immediately cancelled; instead, a cancellation request is recorded and coordinator_1@connectsphere.com is notified to action it</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B230" s="2" t="inlineStr">
-        <is>
-          <t>E11-S01</t>
-        </is>
-      </c>
-      <c r="C230" s="2" t="inlineStr">
-        <is>
-          <t>E11-S01 - Scenario 1 (Status change notified)</t>
-        </is>
-      </c>
-      <c r="D230" s="2" t="inlineStr">
-        <is>
-          <t>2 - Happy Path</t>
-        </is>
-      </c>
-      <c r="E230" s="2" t="inlineStr">
-        <is>
-          <t>TC_E11S01_01</t>
-        </is>
-      </c>
-      <c r="F230" s="2" t="inlineStr">
-        <is>
-          <t>Verify that a user linked to an event should be notified when its status changes or a booking decision is made, with details of what/when/which event</t>
-        </is>
-      </c>
-      <c r="G230" s="2" t="inlineStr">
-        <is>
-          <t>organiser_a@clienta.com is linked to event "Annual Tech Summit", currently "Under Review"</t>
-        </is>
-      </c>
-      <c r="H230" s="2" t="inlineStr">
-        <is>
-          <t>1. As coordinator_1@connectsphere.com, approve request "Annual Tech Summit" (status -&gt; Approved)
-  2. Log in as organiser_a@clienta.com and open notifications</t>
-        </is>
-      </c>
-      <c r="I230" s="2" t="inlineStr">
-        <is>
-          <t>Event: Annual Tech Summit | Change: Under Review -&gt; Approved</t>
-        </is>
-      </c>
-      <c r="J230" s="2" t="inlineStr">
-        <is>
-          <t>A notification is received stating the status changed to "Approved", the time of the change, and that it concerns "Annual Tech Summit"</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B231" s="2" t="inlineStr">
-        <is>
-          <t>E11-S01</t>
-        </is>
-      </c>
-      <c r="C231" s="2" t="inlineStr">
-        <is>
-          <t>E11-S01 - Scenario 2 (All affected parties notified)</t>
-        </is>
-      </c>
-      <c r="D231" s="2" t="inlineStr">
-        <is>
-          <t>2 - Happy Path</t>
-        </is>
-      </c>
-      <c r="E231" s="2" t="inlineStr">
-        <is>
-          <t>TC_E11S01_02</t>
-        </is>
-      </c>
-      <c r="F231" s="2" t="inlineStr">
-        <is>
-          <t>Verify that effective date, time or venue changes follow the approved recipient matrix</t>
-        </is>
-      </c>
-      <c r="G231" s="2" t="inlineStr">
-        <is>
-          <t>Event "Annual Tech Summit" the event has organiser_a@clienta.com, venue_staff_1@connectsphere.com, and tech_support_1@connectsphere.com assigned, and attendee_a@example.com registered; attendee_b@example.com is waitlisted and coordinator_1@connectsphere.com is the assigned Coordinator</t>
-        </is>
-      </c>
-      <c r="H231" s="2" t="inlineStr">
-        <is>
-          <t>1. As coordinator_1@connectsphere.com, change the event's venue
-  2. Check notifications for organiser_a@clienta.com, venue_staff_1@connectsphere.com, tech_support_1@connectsphere.com, and attendee_a@example.com</t>
-        </is>
-      </c>
-      <c r="I231" s="2" t="inlineStr">
-        <is>
-          <t>Changed field: Venue</t>
-        </is>
-      </c>
-      <c r="J231" s="2" t="inlineStr">
-        <is>
-          <t>The Organiser, assigned Venue Staff, assigned Technical Support Staff, registered Attendee and waitlisted Attendee receive a notification. The acting Coordinator receives no self-notification. If another authorized actor or a system operation makes the change, the assigned Coordinator is included. Venue-move tests include responsible staff for both the old and new venues. Backend resolver fixtures are not evidence that the venue-assignment workflow is implemented.</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B232" s="2" t="inlineStr">
-        <is>
-          <t>E11-S01</t>
-        </is>
-      </c>
-      <c r="C232" s="2" t="inlineStr">
-        <is>
-          <t>E11-S01 - Scenario 3 (Unaffected users not notified)</t>
-        </is>
-      </c>
-      <c r="D232" s="2" t="inlineStr">
-        <is>
-          <t>4 - Negative</t>
-        </is>
-      </c>
-      <c r="E232" s="2" t="inlineStr">
-        <is>
-          <t>TC_E11S01_03</t>
-        </is>
-      </c>
-      <c r="F232" s="2" t="inlineStr">
-        <is>
-          <t>Verify that a user whose responsibilities are unaffected by a change should not be notified</t>
-        </is>
-      </c>
-      <c r="G232" s="2" t="inlineStr">
-        <is>
-          <t>Event "Annual Tech Summit" the event's Description field is about to be edited; venue_staff_1@connectsphere.com has no responsibility tied to the Description field</t>
-        </is>
-      </c>
-      <c r="H232" s="2" t="inlineStr">
-        <is>
-          <t>1. As organiser_a@clienta.com, edit the Description field only
-  2. Check venue_staff_1@connectsphere.com's notifications</t>
-        </is>
-      </c>
-      <c r="I232" s="2" t="inlineStr">
-        <is>
-          <t>Changed field: Description only</t>
-        </is>
-      </c>
-      <c r="J232" s="2" t="inlineStr">
-        <is>
-          <t>venue_staff_1@connectsphere.com receives no notification, since the Description change does not affect their responsibilities</t>
         </is>
       </c>
     </row>
@@ -12622,133 +12631,286 @@
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
+          <t>E11-S01 - Scenario 1 (Status change notified)</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>2 - Happy Path</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>TC_E11S01_01</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>Verify that a user linked to an event should be notified when its status changes or a booking decision is made, with details of what/when/which event</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>organiser_a@clienta.com is linked to event "Annual Tech Summit", currently "Under Review"</t>
+        </is>
+      </c>
+      <c r="H233" s="2" t="inlineStr">
+        <is>
+          <t>1. As coordinator_1@connectsphere.com, approve request "Annual Tech Summit" (status -&gt; Approved)
+  2. Log in as organiser_a@clienta.com and open notifications</t>
+        </is>
+      </c>
+      <c r="I233" s="2" t="inlineStr">
+        <is>
+          <t>Event: Annual Tech Summit | Change: Under Review -&gt; Approved</t>
+        </is>
+      </c>
+      <c r="J233" s="2" t="inlineStr">
+        <is>
+          <t>A notification is received stating the status changed to "Approved", the time of the change, and that it concerns "Annual Tech Summit"</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>E11-S01</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>E11-S01 - Scenario 2 (All affected parties notified)</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>2 - Happy Path</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>TC_E11S01_02</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>Verify that effective date, time or venue changes follow the approved recipient matrix</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="inlineStr">
+        <is>
+          <t>Event "Annual Tech Summit" the event has organiser_a@clienta.com, venue_staff_1@connectsphere.com, and tech_support_1@connectsphere.com assigned, and attendee_a@example.com registered; attendee_b@example.com is waitlisted and coordinator_1@connectsphere.com is the assigned Coordinator</t>
+        </is>
+      </c>
+      <c r="H234" s="2" t="inlineStr">
+        <is>
+          <t>1. As coordinator_1@connectsphere.com, change the event's venue
+  2. Check notifications for organiser_a@clienta.com, venue_staff_1@connectsphere.com, tech_support_1@connectsphere.com, and attendee_a@example.com</t>
+        </is>
+      </c>
+      <c r="I234" s="2" t="inlineStr">
+        <is>
+          <t>Changed field: Venue</t>
+        </is>
+      </c>
+      <c r="J234" s="2" t="inlineStr">
+        <is>
+          <t>The Organiser, assigned Venue Staff, assigned Technical Support Staff, registered Attendee and waitlisted Attendee receive a notification. The acting Coordinator receives no self-notification. If another authorized actor or a system operation makes the change, the assigned Coordinator is included. Venue-move tests include responsible staff for both the old and new venues. Backend resolver fixtures are not evidence that the venue-assignment workflow is implemented.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>E11-S01</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>E11-S01 - Scenario 3 (Unaffected users not notified)</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>4 - Negative</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>TC_E11S01_03</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>Verify that a user whose responsibilities are unaffected by a change should not be notified</t>
+        </is>
+      </c>
+      <c r="G235" s="2" t="inlineStr">
+        <is>
+          <t>Event "Annual Tech Summit" the event's Description field is about to be edited; venue_staff_1@connectsphere.com has no responsibility tied to the Description field</t>
+        </is>
+      </c>
+      <c r="H235" s="2" t="inlineStr">
+        <is>
+          <t>1. As organiser_a@clienta.com, edit the Description field only
+  2. Check venue_staff_1@connectsphere.com's notifications</t>
+        </is>
+      </c>
+      <c r="I235" s="2" t="inlineStr">
+        <is>
+          <t>Changed field: Description only</t>
+        </is>
+      </c>
+      <c r="J235" s="2" t="inlineStr">
+        <is>
+          <t>venue_staff_1@connectsphere.com receives no notification, since the Description change does not affect their responsibilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>E11-S01</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
           <t>E11-S01 - Scenario 4 (Delivered in-app and by email)</t>
         </is>
       </c>
-      <c r="D233" s="2" t="inlineStr">
+      <c r="D236" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E233" s="2" t="inlineStr">
+      <c r="E236" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_05</t>
         </is>
       </c>
-      <c r="F233" s="2" t="inlineStr">
+      <c r="F236" s="2" t="inlineStr">
         <is>
           <t>Verify that a generated notification should appear in the system and also be sent to the user's registered email address</t>
         </is>
       </c>
-      <c r="G233" s="2" t="inlineStr">
+      <c r="G236" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com's registered email is organiser_a@clienta.com; a notification-triggering status change is about to occur on their event</t>
         </is>
       </c>
-      <c r="H233" s="2" t="inlineStr">
+      <c r="H236" s="2" t="inlineStr">
         <is>
           <t>1. Trigger a status change on organiser_a@clienta.com's event
   2. Log in as organiser_a@clienta.com and check the in-app notification list
   3. Check the inbox for organiser_a@clienta.com</t>
         </is>
       </c>
-      <c r="I233" s="2" t="inlineStr">
+      <c r="I236" s="2" t="inlineStr">
         <is>
           <t>Registered email: organiser_a@clienta.com</t>
         </is>
       </c>
-      <c r="J233" s="2" t="inlineStr">
+      <c r="J236" s="2" t="inlineStr">
         <is>
           <t>The notification appears in the in-app notification list, and an equivalent email is also delivered to organiser_a@clienta.com's inbox</t>
         </is>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" s="2" t="n">
+    <row r="237">
+      <c r="A237" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B234" s="2" t="inlineStr">
+      <c r="B237" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C234" s="2" t="inlineStr">
+      <c r="C237" s="2" t="inlineStr">
         <is>
           <t>E11-S01 - Scenario 5 (Unread notifications distinguished)</t>
         </is>
       </c>
-      <c r="D234" s="2" t="inlineStr">
+      <c r="D237" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E234" s="2" t="inlineStr">
+      <c r="E237" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_06</t>
         </is>
       </c>
-      <c r="F234" s="2" t="inlineStr">
+      <c r="F237" s="2" t="inlineStr">
         <is>
           <t>Verify that opening the notification list with several unread notifications should show them newest first with unread ones distinguished</t>
         </is>
       </c>
-      <c r="G234" s="2" t="inlineStr">
+      <c r="G237" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com has 3 notifications on 09/09/2026: 08:00 (read), 10:00 (unread), 14:00 (unread)</t>
         </is>
       </c>
-      <c r="H234" s="2" t="inlineStr">
+      <c r="H237" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open the notification list</t>
         </is>
       </c>
-      <c r="I234" s="2" t="inlineStr">
+      <c r="I237" s="2" t="inlineStr">
         <is>
           <t>Notifications: 08:00 (read), 10:00 (unread), 14:00 (unread)</t>
         </is>
       </c>
-      <c r="J234" s="2" t="inlineStr">
+      <c r="J237" s="2" t="inlineStr">
         <is>
           <t>Notifications are listed newest first (14:00, then 10:00, then 08:00), with the 14:00 and 10:00 entries visually marked as unread and 08:00 shown as read</t>
         </is>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" s="2" t="n">
+    <row r="238">
+      <c r="A238" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B235" s="2" t="inlineStr">
+      <c r="B238" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C235" s="2" t="inlineStr">
+      <c r="C238" s="2" t="inlineStr">
         <is>
           <t>E11-S01 - Scenario 6 (Marked as read)</t>
         </is>
       </c>
-      <c r="D235" s="2" t="inlineStr">
+      <c r="D238" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E235" s="2" t="inlineStr">
+      <c r="E238" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_07</t>
         </is>
       </c>
-      <c r="F235" s="2" t="inlineStr">
+      <c r="F238" s="2" t="inlineStr">
         <is>
           <t>Verify that opening an unread notification should mark it as read</t>
         </is>
       </c>
-      <c r="G235" s="2" t="inlineStr">
+      <c r="G238" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com has an unread notification from 10:00 on 09/09/2026</t>
         </is>
       </c>
-      <c r="H235" s="2" t="inlineStr">
+      <c r="H238" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open the notification list
@@ -12756,52 +12918,52 @@
   4. Return to the notification list</t>
         </is>
       </c>
-      <c r="I235" s="2" t="inlineStr">
+      <c r="I238" s="2" t="inlineStr">
         <is>
           <t>Notification: 10:00 on 09/09/2026 (initially unread)</t>
         </is>
       </c>
-      <c r="J235" s="2" t="inlineStr">
+      <c r="J238" s="2" t="inlineStr">
         <is>
           <t>The 10:00 notification is now shown as read (no longer marked unread) in the list</t>
         </is>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" s="2" t="n">
+    <row r="239">
+      <c r="A239" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B236" s="2" t="inlineStr">
+      <c r="B239" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C236" s="2" t="inlineStr">
+      <c r="C239" s="2" t="inlineStr">
         <is>
           <t>E11-S01 · Scenario 5 (Delivered in-app and by email) · ADR-006</t>
         </is>
       </c>
-      <c r="D236" s="2" t="inlineStr">
+      <c r="D239" s="2" t="inlineStr">
         <is>
           <t>4 - Negative (third-party unavailable)</t>
         </is>
       </c>
-      <c r="E236" s="2" t="inlineStr">
+      <c r="E239" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_08</t>
         </is>
       </c>
-      <c r="F236" s="2" t="inlineStr">
+      <c r="F239" s="2" t="inlineStr">
         <is>
           <t>Verify that an unreachable email provider does not affect the business change or the in-app notification</t>
         </is>
       </c>
-      <c r="G236" s="2" t="inlineStr">
+      <c r="G239" s="2" t="inlineStr">
         <is>
           <t>Event EVT-2003 has an assigned Coordinator coord_a@connectsphere.com. The email provider endpoint is configured to an unreachable host so every SMTP attempt fails</t>
         </is>
       </c>
-      <c r="H236" s="2" t="inlineStr">
+      <c r="H239" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as Venue Staff and approve the pending venue booking for EVT-2003
  2. Confirm the booking status has changed
@@ -12809,52 +12971,52 @@
  4. Inspect the delivery records for that notification</t>
         </is>
       </c>
-      <c r="I236" s="2" t="inlineStr">
+      <c r="I239" s="2" t="inlineStr">
         <is>
           <t>SMTP host: unreachable · Notification: venue booking approved</t>
         </is>
       </c>
-      <c r="J236" s="2" t="inlineStr">
+      <c r="J239" s="2" t="inlineStr">
         <is>
           <t>The booking is Confirmed and the change persists. The in-app notification appears for the Coordinator. The email delivery row is marked failed with a recorded reason. The business transaction is not rolled back by the email failure</t>
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" s="2" t="n">
+    <row r="240">
+      <c r="A240" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B237" s="2" t="inlineStr">
+      <c r="B240" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C237" s="2" t="inlineStr">
+      <c r="C240" s="2" t="inlineStr">
         <is>
           <t>E11-S01 · Scenario 1 (Status change notified) · ADR-006 outbox guarantee</t>
         </is>
       </c>
-      <c r="D237" s="2" t="inlineStr">
+      <c r="D240" s="2" t="inlineStr">
         <is>
           <t>4 - Negative (transaction rollback)</t>
         </is>
       </c>
-      <c r="E237" s="2" t="inlineStr">
+      <c r="E240" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_09</t>
         </is>
       </c>
-      <c r="F237" s="2" t="inlineStr">
+      <c r="F240" s="2" t="inlineStr">
         <is>
           <t>Verify that a rolled-back business transaction publishes no notification</t>
         </is>
       </c>
-      <c r="G237" s="2" t="inlineStr">
+      <c r="G240" s="2" t="inlineStr">
         <is>
           <t>Event EVT-2004 is at status Under Review. A fault is injected so that the approval transaction fails after the notification delivery rows are written but before commit</t>
         </is>
       </c>
-      <c r="H237" s="2" t="inlineStr">
+      <c r="H240" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as the assigned Event Coordinator
  2. Approve EVT-2004, triggering the injected failure
@@ -12862,164 +13024,14 @@
  4. Inspect the job queue and the Organiser's notification list</t>
         </is>
       </c>
-      <c r="I237" s="2" t="inlineStr">
+      <c r="I240" s="2" t="inlineStr">
         <is>
           <t>Event: EVT-2004 · Injected failure point: after delivery rows written, before commit</t>
         </is>
       </c>
-      <c r="J237" s="2" t="inlineStr">
+      <c r="J240" s="2" t="inlineStr">
         <is>
           <t>The event remains at Under Review. No delivery row is persisted, nothing is published to the queue, and the Organiser receives no in-app notification and no email. Only committed deliveries are ever published</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B238" s="2" t="inlineStr">
-        <is>
-          <t>E11-S01</t>
-        </is>
-      </c>
-      <c r="C238" s="2" t="inlineStr">
-        <is>
-          <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
-        </is>
-      </c>
-      <c r="D238" s="2" t="inlineStr">
-        <is>
-          <t>3 - Integration / regression</t>
-        </is>
-      </c>
-      <c r="E238" s="2" t="inlineStr">
-        <is>
-          <t>TC_E11S01_10</t>
-        </is>
-      </c>
-      <c r="F238" s="2" t="inlineStr">
-        <is>
-          <t>Apply the approved role/change recipient matrix</t>
-        </is>
-      </c>
-      <c r="G238" s="2" t="inlineStr">
-        <is>
-          <t>The event has active links to all six recipient groups and a public snapshot.</t>
-        </is>
-      </c>
-      <c r="H238" s="2" t="inlineStr">
-        <is>
-          <t>1. Trigger each internal status, booking, equipment, public status, arrangement, place-release and description-only change through the selector.</t>
-        </is>
-      </c>
-      <c r="I238" s="2" t="inlineStr">
-        <is>
-          <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
-        </is>
-      </c>
-      <c r="J238" s="2" t="inlineStr">
-        <is>
-          <t>Recipient sets match the E11-S01 matrix; internal decisions do not reach Attendees; initial Planning differs from Confirmed-to-Planning.</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B239" s="2" t="inlineStr">
-        <is>
-          <t>E11-S01</t>
-        </is>
-      </c>
-      <c r="C239" s="2" t="inlineStr">
-        <is>
-          <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
-        </is>
-      </c>
-      <c r="D239" s="2" t="inlineStr">
-        <is>
-          <t>3 - Integration / regression</t>
-        </is>
-      </c>
-      <c r="E239" s="2" t="inlineStr">
-        <is>
-          <t>TC_E11S01_11</t>
-        </is>
-      </c>
-      <c r="F239" s="2" t="inlineStr">
-        <is>
-          <t>Suppress self-notifications and duplicate recipient links</t>
-        </is>
-      </c>
-      <c r="G239" s="2" t="inlineStr">
-        <is>
-          <t>A user is both the actor and a candidate recipient; duplicated staff links exist.</t>
-        </is>
-      </c>
-      <c r="H239" s="2" t="inlineStr">
-        <is>
-          <t>1. Select recipients for an arrangement change and an actor-made booking decision.</t>
-        </is>
-      </c>
-      <c r="I239" s="2" t="inlineStr">
-        <is>
-          <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
-        </is>
-      </c>
-      <c r="J239" s="2" t="inlineStr">
-        <is>
-          <t>The actor receives no routine self-notification; every remaining user appears once; system changes have no excluded actor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B240" s="2" t="inlineStr">
-        <is>
-          <t>E11-S01</t>
-        </is>
-      </c>
-      <c r="C240" s="2" t="inlineStr">
-        <is>
-          <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
-        </is>
-      </c>
-      <c r="D240" s="2" t="inlineStr">
-        <is>
-          <t>3 - Integration / regression</t>
-        </is>
-      </c>
-      <c r="E240" s="2" t="inlineStr">
-        <is>
-          <t>TC_E11S01_12</t>
-        </is>
-      </c>
-      <c r="F240" s="2" t="inlineStr">
-        <is>
-          <t>Preserve before/after recipients during cancellation and venue moves</t>
-        </is>
-      </c>
-      <c r="G240" s="2" t="inlineStr">
-        <is>
-          <t>An event has active bookings, assigned staff, registered and waitlisted Attendees.</t>
-        </is>
-      </c>
-      <c r="H240" s="2" t="inlineStr">
-        <is>
-          <t>1. Capture its audience, release links during cancellation or replace the venue, then call the hook with both snapshots.</t>
-        </is>
-      </c>
-      <c r="I240" s="2" t="inlineStr">
-        <is>
-          <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
-        </is>
-      </c>
-      <c r="J240" s="2" t="inlineStr">
-        <is>
-          <t>Cancellation notifies the pre-release audience. Venue moves include responsible staff at both venues. These are hook-contract tests until the owning workflows integrate.</t>
         </is>
       </c>
     </row>
@@ -13044,22 +13056,22 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>TC_E11S01_13</t>
+          <t>TC_E11S01_10</t>
         </is>
       </c>
       <c r="F241" s="2" t="inlineStr">
         <is>
-          <t>Expose missing Venue Staff assignments without an unsafe fallback</t>
+          <t>Apply the approved role/change recipient matrix</t>
         </is>
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>No explicit venue assignment adapter is available; a booking has a decided_by actor and unrelated Venue Staff accounts exist.</t>
+          <t>The event has active links to all six recipient groups and a public snapshot.</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
-          <t>1. Capture the audience and select booking-request recipients.</t>
+          <t>1. Trigger each internal status, booking, equipment, public status, arrangement, place-release and description-only change through the selector.</t>
         </is>
       </c>
       <c r="I241" s="2" t="inlineStr">
@@ -13069,7 +13081,7 @@
       </c>
       <c r="J241" s="2" t="inlineStr">
         <is>
-          <t>Venue Staff recipients are unresolved, the venue IDs are reported, and neither decided_by nor all Venue Staff is substituted.</t>
+          <t>Recipient sets match the E11-S01 matrix; internal decisions do not reach Attendees; initial Planning differs from Confirmed-to-Planning.</t>
         </is>
       </c>
     </row>
@@ -13094,22 +13106,22 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>TC_E11S01_14</t>
+          <t>TC_E11S01_11</t>
         </is>
       </c>
       <c r="F242" s="2" t="inlineStr">
         <is>
-          <t>Protect attendee notification content and membership boundaries</t>
+          <t>Suppress self-notifications and duplicate recipient links</t>
         </is>
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>The internal event title differs from its publication; registered, waitlisted, withdrawn, inactive and unrelated users exist.</t>
+          <t>A user is both the actor and a candidate recipient; duplicated staff links exist.</t>
         </is>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
-          <t>1. Apply an effective date change; inspect notification messages and retained email payloads. Also select recipients for an unpublished event.</t>
+          <t>1. Select recipients for an arrangement change and an actor-made booking decision.</t>
         </is>
       </c>
       <c r="I242" s="2" t="inlineStr">
@@ -13119,7 +13131,7 @@
       </c>
       <c r="J242" s="2" t="inlineStr">
         <is>
-          <t>Only eligible linked active users are selected. Attendees receive the published event name and fixed public change description; no internal title/reason/comment leaks. Unpublished events produce no attendee notice.</t>
+          <t>The actor receives no routine self-notification; every remaining user appears once; system changes have no excluded actor.</t>
         </is>
       </c>
     </row>
@@ -13144,22 +13156,22 @@
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>TC_E11S01_15</t>
+          <t>TC_E11S01_12</t>
         </is>
       </c>
       <c r="F243" s="2" t="inlineStr">
         <is>
-          <t>Deduplicate concurrent notification-hook retries</t>
+          <t>Preserve before/after recipients during cancellation and venue moves</t>
         </is>
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>Two transactions use the same event, stable change ID and recipient snapshot.</t>
+          <t>An event has active bookings, assigned staff, registered and waitlisted Attendees.</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
-          <t>1. Call the notification hook concurrently and commit both attempts.</t>
+          <t>1. Capture its audience, release links during cancellation or replace the venue, then call the hook with both snapshots.</t>
         </is>
       </c>
       <c r="I243" s="2" t="inlineStr">
@@ -13169,7 +13181,7 @@
       </c>
       <c r="J243" s="2" t="inlineStr">
         <is>
-          <t>Exactly one in-app row and one email-delivery row exist per recipient for the logical change. A new change ID identifies a different business change.</t>
+          <t>Cancellation notifies the pre-release audience. Venue moves include responsible staff at both venues. These are hook-contract tests until the owning workflows integrate.</t>
         </is>
       </c>
     </row>
@@ -13194,22 +13206,22 @@
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>TC_E11S01_16</t>
+          <t>TC_E11S01_13</t>
         </is>
       </c>
       <c r="F244" s="2" t="inlineStr">
         <is>
-          <t>Keep uncommitted notifications invisible and roll back all writes</t>
+          <t>Expose missing Venue Staff assignments without an unsafe fallback</t>
         </is>
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>A business transaction has inserted notifications and prepared email delivery rows but has not committed.</t>
+          <t>No explicit venue assignment adapter is available; a booking has a decided_by actor and unrelated Venue Staff accounts exist.</t>
         </is>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
-          <t>1. Read from another connection, then force the business transaction to roll back.</t>
+          <t>1. Capture the audience and select booking-request recipients.</t>
         </is>
       </c>
       <c r="I244" s="2" t="inlineStr">
@@ -13219,169 +13231,163 @@
       </c>
       <c r="J244" s="2" t="inlineStr">
         <is>
-          <t>The other connection cannot observe the uncommitted messages. After rollback no notification or email-delivery row remains.</t>
+          <t>Venue Staff recipients are unresolved, the venue IDs are reported, and neither decided_by nor all Venue Staff is substituted.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>E14-S02</t>
+          <t>E11-S01</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>E14-S02 - Scenario 1 (Status change recorded)</t>
+          <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>2 - Happy Path</t>
+          <t>3 - Integration / regression</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>TC_E14S02_01</t>
+          <t>TC_E11S01_14</t>
         </is>
       </c>
       <c r="F245" s="2" t="inlineStr">
         <is>
-          <t>Verify that an event status change should be recorded with the actor, action, affected event, and time</t>
+          <t>Protect attendee notification content and membership boundaries</t>
         </is>
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>Request "Annual Tech Summit" has status "Under Review"</t>
+          <t>The internal event title differs from its publication; registered, waitlisted, withdrawn, inactive and unrelated users exist.</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
-          <t>1. As coordinator_1@connectsphere.com, approve the request (status -&gt; Approved)
-  2. Log in as a System Administrator
-  3. Open the Activity Log and locate the entry</t>
+          <t>1. Apply an effective date change; inspect notification messages and retained email payloads. Also select recipients for an unpublished event.</t>
         </is>
       </c>
       <c r="I245" s="2" t="inlineStr">
         <is>
-          <t>Event: Annual Tech Summit | Action: Approve</t>
+          <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
         </is>
       </c>
       <c r="J245" s="2" t="inlineStr">
         <is>
-          <t>An entry is recorded with actor = coordinator_1@connectsphere.com, action = "Status changed to Approved", event = Annual Tech Summit, and a timestamp</t>
+          <t>Only eligible linked active users are selected. Attendees receive the published event name and fixed public change description; no internal title/reason/comment leaks. Unpublished events produce no attendee notice.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>E14-S02</t>
+          <t>E11-S01</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>E14-S02 - Scenario 2 (Access denial recorded)</t>
+          <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>2 - Happy Path</t>
+          <t>3 - Integration / regression</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>TC_E14S02_02</t>
+          <t>TC_E11S01_15</t>
         </is>
       </c>
       <c r="F246" s="2" t="inlineStr">
         <is>
-          <t>Verify that a denied access attempt should be recorded with the user, target, and time</t>
+          <t>Deduplicate concurrent notification-hook retries</t>
         </is>
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>organiser_a@clienta.com is linked to Client A; event EVT-B01 belongs to Client B</t>
+          <t>Two transactions use the same event, stable change ID and recipient snapshot.</t>
         </is>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
-          <t>1. As organiser_a@clienta.com, attempt to access EVT-B01 directly
-  2. Log in as a System Administrator
-  3. Check the Activity Log</t>
+          <t>1. Call the notification hook concurrently and commit both attempts.</t>
         </is>
       </c>
       <c r="I246" s="2" t="inlineStr">
         <is>
-          <t>User: organiser_a@clienta.com | Target: EVT-B01</t>
+          <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
         </is>
       </c>
       <c r="J246" s="2" t="inlineStr">
         <is>
-          <t>An entry is recorded with user = organiser_a@clienta.com, target = EVT-B01, action = "Access Denied", and a timestamp</t>
+          <t>Exactly one in-app row and one email-delivery row exist per recipient for the logical change. A new change ID identifies a different business change.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>E14-S02</t>
+          <t>E11-S01</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>E14-S02 - Scenario 3 (Booking decision recorded)</t>
+          <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>2 - Happy Path</t>
+          <t>3 - Integration / regression</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>TC_E14S02_03</t>
+          <t>TC_E11S01_16</t>
         </is>
       </c>
       <c r="F247" s="2" t="inlineStr">
         <is>
-          <t>Verify that an approved venue booking should be recorded with the actor, action, affected records, and time</t>
+          <t>Keep uncommitted notifications invisible and roll back all writes</t>
         </is>
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>A booking request for Venue Z is pending</t>
+          <t>A business transaction has inserted notifications and prepared email delivery rows but has not committed.</t>
         </is>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
-          <t>1. As Venue Staff, approve the booking request
-  2. Log in as a System Administrator
-  3. Check the Activity Log</t>
+          <t>1. Read from another connection, then force the business transaction to roll back.</t>
         </is>
       </c>
       <c r="I247" s="2" t="inlineStr">
         <is>
-          <t>Venue: Venue Z | Action: Approve Booking</t>
+          <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
         </is>
       </c>
       <c r="J247" s="2" t="inlineStr">
         <is>
-          <t>An entry is recorded with the actor, action ("Booking Approved"), the affected booking/event, and a timestamp</t>
+          <t>The other connection cannot observe the uncommitted messages. After rollback no notification or email-delivery row remains.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
@@ -13390,7 +13396,7 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>E14-S02 - Scenario 4 (Deactivation recorded)</t>
+          <t>E14-S02 - Scenario 1 (Status change recorded; T-66, T-67)</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
@@ -13400,40 +13406,41 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>TC_E14S02_04</t>
+          <t>TC_E14S02_01</t>
         </is>
       </c>
       <c r="F248" s="2" t="inlineStr">
         <is>
-          <t>Verify that an account deactivation should be recorded in the activity log</t>
+          <t>Verify that an event status change should be recorded with the actor, action, affected event, and time</t>
         </is>
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>organiser_a@clienta.com is signed in</t>
+          <t>Request "Annual Tech Summit" has status "Under Review"; coordinator_1@connectsphere.com is an Event Coordinator permitted to view and approve it</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
-          <t>1. Deactivate the account
-  2. Log in as a System Administrator
-  3. Check the Activity Log</t>
+          <t>1. As coordinator_1@connectsphere.com, approve the request (status -&gt; Approved)
+2. Open the approved event's existing detail page as that Coordinator
+3. Locate the status-change entry in its Activity log
+4. Compare the displayed actor, action and timestamp with the completed change and affected event</t>
         </is>
       </c>
       <c r="I248" s="2" t="inlineStr">
         <is>
-          <t>Account: organiser_a@clienta.com</t>
+          <t>Event: Annual Tech Summit | Action: Approve</t>
         </is>
       </c>
       <c r="J248" s="2" t="inlineStr">
         <is>
-          <t>An entry is recorded showing the account deactivation with actor and timestamp</t>
+          <t>An entry is recorded with actor = coordinator_1@connectsphere.com, action = "Status changed to Approved", event = Annual Tech Summit, and a timestamp; the Event Coordinator can read it on that event under existing access rules, without an Administrator role or global audit screen</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
@@ -13442,46 +13449,45 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>E14-S02 - Scenario 5 (Log entries immutable)</t>
+          <t>E14-S02 - Scenario 2 (Access denial recorded; T-66, T-67)</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>4 - Negative</t>
+          <t>2 - Happy Path</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>TC_E14S02_05</t>
+          <t>TC_E14S02_02</t>
         </is>
       </c>
       <c r="F249" s="2" t="inlineStr">
         <is>
-          <t>Verify that any attempt to edit or delete an activity log entry should be refused</t>
+          <t>Verify that a denied access attempt should be recorded with the user, target, and time</t>
         </is>
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>A log entry exists: Event = Annual Tech Summit, Action = "Status changed to Approved", Actor = coordinator_1@connectsphere.com (created in TC_E14S02_01)</t>
+          <t>organiser_a@clienta.com is linked to Client A; event EVT-B01 belongs to Client B; the tester has read access to a controlled test database</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
-          <t>1. Log in as a System Administrator
-  2. Open the Activity Log and locate the entry for Event = Annual Tech Summit, Action = "Status changed to Approved"
-  3. Attempt to edit the entry's Action field to "Status changed to Rejected"
-  4. Attempt to delete the same entry
-  5. If no UI path exists for either action, attempt the same edit and delete via a direct API call to the log entry's ID</t>
+          <t>1. As organiser_a@clienta.com, attempt to access EVT-B01 directly
+2. Confirm the request is refused
+3. As the tester, query audit_logs in the controlled test database for that user, target and attempt time
+4. Check the matching denial row's user, target, action and timestamp</t>
         </is>
       </c>
       <c r="I249" s="2" t="inlineStr">
         <is>
-          <t>Target log entry: Event = Annual Tech Summit, Action = "Status changed to Approved" | Attempted edit: Action -&gt; "Status changed to Rejected"</t>
+          <t>User: organiser_a@clienta.com | Target: EVT-B01</t>
         </is>
       </c>
       <c r="J249" s="2" t="inlineStr">
         <is>
-          <t>Both the edit and delete attempts are refused; no UI control exists to modify or remove a log entry, and the direct API call returns an authorization/forbidden error with the entry left unchanged</t>
+          <t>An entry is recorded with user = organiser_a@clienta.com, target = EVT-B01, action = "Access Denied", and a timestamp</t>
         </is>
       </c>
     </row>
@@ -13496,7 +13502,7 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>E14-S02 - Scenario 3 (Booking decision recorded)</t>
+          <t>E14-S02 - former Scenario 3 (transferred to E06-S04 Scenario 4 by T-67; see TC_E06S04_04)</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
@@ -13506,12 +13512,12 @@
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>TC_E14S02_06</t>
+          <t>TC_E14S02_03</t>
         </is>
       </c>
       <c r="F250" s="2" t="inlineStr">
         <is>
-          <t>Verify that a rejected venue booking should be recorded with the actor, action, affected records, and time</t>
+          <t>[RETIRED — moved to TC_E06S04_04 by T-67] Verify that an approved venue booking should be recorded with the actor, action, affected records, and time</t>
         </is>
       </c>
       <c r="G250" s="2" t="inlineStr">
@@ -13521,25 +13527,24 @@
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
-          <t>1. As Venue Staff, reject the booking request with reason "Venue unavailable for maintenance"
-  2. Log in as a System Administrator
-  3. Check the Activity Log</t>
+          <t>1. Do not execute this retired case; use TC_E06S04_04 under E06-S04 Scenario 4.
+2. Refer to the earlier dated workbook for the original steps.</t>
         </is>
       </c>
       <c r="I250" s="2" t="inlineStr">
         <is>
-          <t>Venue: Venue Z | Action: Reject Booking | Reason: Venue unavailable for maintenance</t>
+          <t>Venue: Venue Z | Action: Approve Booking</t>
         </is>
       </c>
       <c r="J250" s="2" t="inlineStr">
         <is>
-          <t>An entry is recorded with the actor, action ("Booking Rejected"), the affected booking/event, and a timestamp</t>
+          <t>An entry is recorded with the actor, action ("Booking Approved"), the affected booking/event, and a timestamp</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
@@ -13548,7 +13553,7 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>E14-S02 - Scenario 3 (Booking decision recorded)</t>
+          <t>E14-S02 - Scenario 4 (Deactivation recorded; T-66, T-67)</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
@@ -13558,34 +13563,34 @@
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>TC_E14S02_07</t>
+          <t>TC_E14S02_04</t>
         </is>
       </c>
       <c r="F251" s="2" t="inlineStr">
         <is>
-          <t>Verify that a released venue booking should be recorded with the actor, action, affected records, and time</t>
+          <t>Verify that an account deactivation should be recorded in the activity log</t>
         </is>
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>Venue Z has a confirmed booking for event "Annual Tech Summit"</t>
+          <t>organiser_a@clienta.com is signed in; the tester has read access to a controlled test database</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
-          <t>1. As Venue Staff or Coordinator, release the confirmed booking for Venue Z (e.g. due to event cancellation)
-  2. Log in as a System Administrator
-  3. Check the Activity Log</t>
+          <t>1. As organiser_a@clienta.com, deactivate the account
+2. As the tester, query audit_logs in the controlled test database for that account and action time
+3. Check the matching deactivation row's actor, action and timestamp</t>
         </is>
       </c>
       <c r="I251" s="2" t="inlineStr">
         <is>
-          <t>Venue: Venue Z | Action: Release Booking | Event: Annual Tech Summit</t>
+          <t>Account: organiser_a@clienta.com</t>
         </is>
       </c>
       <c r="J251" s="2" t="inlineStr">
         <is>
-          <t>An entry is recorded with the actor, action ("Booking Released"), the affected booking/event, and a timestamp</t>
+          <t>An entry is recorded showing the account deactivation with actor and timestamp</t>
         </is>
       </c>
     </row>
@@ -13595,151 +13600,307 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
+          <t>E14-S02</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>E14-S02 - Scenario 5 (Log entries immutable; T-66, T-67)</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>4 - Negative</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>TC_E14S02_05</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>Verify that any attempt to edit or delete an activity log entry should be refused</t>
+        </is>
+      </c>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
+          <t>A log entry exists: Event = Annual Tech Summit, Action = "Status changed to Approved", Actor = coordinator_1@connectsphere.com (created in TC_E14S02_01 or an equivalent independent fixture in a disposable test database)</t>
+        </is>
+      </c>
+      <c r="H252" s="2" t="inlineStr">
+        <is>
+          <t>1. As an Event Coordinator permitted to view the event, open its Activity log
+2. Confirm no edit or delete control is offered for the entry
+3. For each existing application role (event_organiser, event_coordinator, venue_staff, technical_support and attendee), attempt direct API update and delete requests against the entry
+4. As the database test harness, attempt UPDATE and DELETE of that entry through the application database connection in separate transactions
+5. Read the original entry after each refused attempt to confirm its contents and row remain unchanged</t>
+        </is>
+      </c>
+      <c r="I252" s="2" t="inlineStr">
+        <is>
+          <t>Target log entry: Event = Annual Tech Summit, Action = "Status changed to Approved" | Attempted edit: Action -&gt; "Status changed to Rejected"</t>
+        </is>
+      </c>
+      <c r="J252" s="2" t="inlineStr">
+        <is>
+          <t>All update and delete attempts are refused. Unsupported API methods or routes may return 404/405; protected mutation routes must reject unauthorised requests. No response may represent a successful mutation. The database rejects both operations and the entry remains unchanged. No Administrator role is required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>E14-S02</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>E14-S02 - former Scenario 3 (transferred to E06-S04 Scenario 4 by T-67; see TC_E06S04_05)</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>2 - Happy Path</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>TC_E14S02_06</t>
+        </is>
+      </c>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t>[RETIRED — moved to TC_E06S04_05 by T-67] Verify that a rejected venue booking should be recorded with the actor, action, affected records, and time</t>
+        </is>
+      </c>
+      <c r="G253" s="2" t="inlineStr">
+        <is>
+          <t>A booking request for Venue Z is pending</t>
+        </is>
+      </c>
+      <c r="H253" s="2" t="inlineStr">
+        <is>
+          <t>1. Do not execute this retired case; use TC_E06S04_05 under E06-S04 Scenario 4.
+2. Refer to the earlier dated workbook for the original steps.</t>
+        </is>
+      </c>
+      <c r="I253" s="2" t="inlineStr">
+        <is>
+          <t>Venue: Venue Z | Action: Reject Booking | Reason: Venue unavailable for maintenance</t>
+        </is>
+      </c>
+      <c r="J253" s="2" t="inlineStr">
+        <is>
+          <t>An entry is recorded with the actor, action ("Booking Rejected"), the affected booking/event, and a timestamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>E14-S02</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>E14-S02 - former Scenario 3 (transferred to E06-S04 Scenario 4 by T-67; see TC_E06S04_06)</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>2 - Happy Path</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>TC_E14S02_07</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>[RETIRED — moved to TC_E06S04_06 by T-67] Verify that a released venue booking should be recorded with the actor, action, affected records, and time</t>
+        </is>
+      </c>
+      <c r="G254" s="2" t="inlineStr">
+        <is>
+          <t>Venue Z has a confirmed booking for event "Annual Tech Summit"</t>
+        </is>
+      </c>
+      <c r="H254" s="2" t="inlineStr">
+        <is>
+          <t>1. Do not execute this retired case; use TC_E06S04_06 under E06-S04 Scenario 4.
+2. Refer to the earlier dated workbook for the original steps.</t>
+        </is>
+      </c>
+      <c r="I254" s="2" t="inlineStr">
+        <is>
+          <t>Venue: Venue Z | Action: Release Booking | Event: Annual Tech Summit</t>
+        </is>
+      </c>
+      <c r="J254" s="2" t="inlineStr">
+        <is>
+          <t>An entry is recorded with the actor, action ("Booking Released"), the affected booking/event, and a timestamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
           <t>Definition of Done</t>
         </is>
       </c>
-      <c r="C252" s="2" t="inlineStr">
+      <c r="C255" s="2" t="inlineStr">
         <is>
           <t>Definition of Done · BDR T-51 · Week 1 §8a</t>
         </is>
       </c>
-      <c r="D252" s="2" t="inlineStr">
+      <c r="D255" s="2" t="inlineStr">
         <is>
           <t>3 - Cross-cutting</t>
         </is>
       </c>
-      <c r="E252" s="2" t="inlineStr">
+      <c r="E255" s="2" t="inlineStr">
         <is>
           <t>TC_PERF_01</t>
         </is>
       </c>
-      <c r="F252" s="2" t="inlineStr">
+      <c r="F255" s="2" t="inlineStr">
         <is>
           <t>Verify a venue search returns within the 3-second target on a realistic catalogue</t>
         </is>
       </c>
-      <c r="G252" s="2" t="inlineStr">
+      <c r="G255" s="2" t="inlineStr">
         <is>
           <t>The venue catalogue holds 50 venues with layouts, accessibility features and facilities. 200 confirmed bookings exist across the next 90 days. Coordinator coord_a@connectsphere.com is signed in</t>
         </is>
       </c>
-      <c r="H252" s="2" t="inlineStr">
+      <c r="H255" s="2" t="inlineStr">
         <is>
           <t>1. Open the venue search
  2. Enter date 2026-12-01, time 09:00–11:00, expected attendance 120, layout Theatre, accessibility Step-free access
  3. Start a timer on submit and stop it when results render</t>
         </is>
       </c>
-      <c r="I252" s="2" t="inlineStr">
+      <c r="I255" s="2" t="inlineStr">
         <is>
           <t>50 venues · 200 bookings · elapsed time measured client-side</t>
         </is>
       </c>
-      <c r="J252" s="2" t="inlineStr">
+      <c r="J255" s="2" t="inlineStr">
         <is>
           <t>Results render in under 3 seconds. Record the measured time; if it exceeds 3 seconds the story does not meet the Definition of Done</t>
         </is>
       </c>
     </row>
-    <row r="253">
-      <c r="A253" s="2" t="n">
+    <row r="256">
+      <c r="A256" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B253" s="2" t="inlineStr">
+      <c r="B256" s="2" t="inlineStr">
         <is>
           <t>Definition of Done</t>
         </is>
       </c>
-      <c r="C253" s="2" t="inlineStr">
+      <c r="C256" s="2" t="inlineStr">
         <is>
           <t>Definition of Done · BDR T-51 · Week 1 §8a</t>
         </is>
       </c>
-      <c r="D253" s="2" t="inlineStr">
+      <c r="D256" s="2" t="inlineStr">
         <is>
           <t>3 - Cross-cutting</t>
         </is>
       </c>
-      <c r="E253" s="2" t="inlineStr">
+      <c r="E256" s="2" t="inlineStr">
         <is>
           <t>TC_PERF_02</t>
         </is>
       </c>
-      <c r="F253" s="2" t="inlineStr">
+      <c r="F256" s="2" t="inlineStr">
         <is>
           <t>Verify the venue availability calendar loads within the 3-second target for a busy month</t>
         </is>
       </c>
-      <c r="G253" s="2" t="inlineStr">
+      <c r="G256" s="2" t="inlineStr">
         <is>
           <t>Orchid Hall has 40 confirmed bookings, 5 tentative holds and 3 maintenance blocks within 2026-12-01 to 2026-12-31</t>
         </is>
       </c>
-      <c r="H253" s="2" t="inlineStr">
+      <c r="H256" s="2" t="inlineStr">
         <is>
           <t>1. Open Orchid Hall in the venue catalogue
  2. Select the calendar for December 2026
  3. Start a timer on selection and stop it when all states have rendered</t>
         </is>
       </c>
-      <c r="I253" s="2" t="inlineStr">
+      <c r="I256" s="2" t="inlineStr">
         <is>
           <t>48 calendar entries in one month · elapsed time measured client-side</t>
         </is>
       </c>
-      <c r="J253" s="2" t="inlineStr">
+      <c r="J256" s="2" t="inlineStr">
         <is>
           <t>The calendar renders all Free, Tentative, Confirmed and Blocked states in under 3 seconds</t>
         </is>
       </c>
     </row>
-    <row r="254">
-      <c r="A254" s="2" t="n">
+    <row r="257">
+      <c r="A257" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B254" s="2" t="inlineStr">
+      <c r="B257" s="2" t="inlineStr">
         <is>
           <t>Definition of Done</t>
         </is>
       </c>
-      <c r="C254" s="2" t="inlineStr">
+      <c r="C257" s="2" t="inlineStr">
         <is>
           <t>Definition of Done · BDR T-51 · Week 1 §8a</t>
         </is>
       </c>
-      <c r="D254" s="2" t="inlineStr">
+      <c r="D257" s="2" t="inlineStr">
         <is>
           <t>3 - Cross-cutting</t>
         </is>
       </c>
-      <c r="E254" s="2" t="inlineStr">
+      <c r="E257" s="2" t="inlineStr">
         <is>
           <t>TC_PERF_03</t>
         </is>
       </c>
-      <c r="F254" s="2" t="inlineStr">
+      <c r="F257" s="2" t="inlineStr">
         <is>
           <t>Verify a registration submission completes within the 3-second target near capacity</t>
         </is>
       </c>
-      <c r="G254" s="2" t="inlineStr">
+      <c r="G257" s="2" t="inlineStr">
         <is>
           <t>Event EVT-2001 is Confirmed with Orchid Hall booked, venue capacity 200, and 198 registrations recorded. Attendee attendee_b@example.com is signed in</t>
         </is>
       </c>
-      <c r="H254" s="2" t="inlineStr">
+      <c r="H257" s="2" t="inlineStr">
         <is>
           <t>1. Open event EVT-2001
  2. Submit a registration
  3. Start a timer on submit and stop it when confirmation renders</t>
         </is>
       </c>
-      <c r="I254" s="2" t="inlineStr">
+      <c r="I257" s="2" t="inlineStr">
         <is>
           <t>198 existing registrations · capacity 200 · elapsed time measured client-side</t>
         </is>
       </c>
-      <c r="J254" s="2" t="inlineStr">
+      <c r="J257" s="2" t="inlineStr">
         <is>
           <t>The registration is created and confirmation renders in under 3 seconds, including the capacity check against the booked venue</t>
         </is>

--- a/docs/testing/PROJECT TEST CASES CAA 021026.xlsx
+++ b/docs/testing/PROJECT TEST CASES CAA 021026.xlsx
@@ -4049,7 +4049,7 @@
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>The reason and decision date are shown in plain language (e.g. "Rejected on 10 September 2026 - Requested date unavailable across all venues"); all fields are read-only and cannot be edited</t>
+          <t>The reason and decision date are shown in plain language (e.g. "Rejected on 10 Sept 2026 — Requested date unavailable across all venues", the date as the app writes it); all fields are read-only and cannot be edited</t>
         </is>
       </c>
     </row>
